--- a/songs/TakeOnMe_v1/quelle/struktur-raster.xlsx
+++ b/songs/TakeOnMe_v1/quelle/struktur-raster.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6" collapsed="1">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7" hidden="1" outlineLevel="2">
       <c r="A7" s="4" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="n"/>
@@ -570,7 +570,7 @@
     </row>
     <row r="8" hidden="1" outlineLevel="2">
       <c r="A8" s="4" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6" t="n"/>
@@ -581,7 +581,7 @@
     </row>
     <row r="9" hidden="1" outlineLevel="2">
       <c r="A9" s="4" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
@@ -592,7 +592,7 @@
     </row>
     <row r="10" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6" t="n"/>
@@ -603,7 +603,7 @@
     </row>
     <row r="11" hidden="1" outlineLevel="2">
       <c r="A11" s="4" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
@@ -614,7 +614,7 @@
     </row>
     <row r="12" hidden="1" outlineLevel="2">
       <c r="A12" s="4" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="n"/>
@@ -625,7 +625,7 @@
     </row>
     <row r="13" hidden="1" outlineLevel="2">
       <c r="A13" s="4" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6" t="n"/>
@@ -636,7 +636,7 @@
     </row>
     <row r="14" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="n"/>
@@ -647,7 +647,7 @@
     </row>
     <row r="15" hidden="1" outlineLevel="2">
       <c r="A15" s="4" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6" t="n"/>
@@ -658,7 +658,7 @@
     </row>
     <row r="16" hidden="1" outlineLevel="2">
       <c r="A16" s="4" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="n"/>
@@ -669,7 +669,7 @@
     </row>
     <row r="17" hidden="1" outlineLevel="2">
       <c r="A17" s="4" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6" t="n"/>
@@ -680,7 +680,7 @@
     </row>
     <row r="18" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6" t="n"/>
@@ -691,7 +691,7 @@
     </row>
     <row r="19" hidden="1" outlineLevel="2">
       <c r="A19" s="4" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6" t="n"/>
@@ -702,7 +702,7 @@
     </row>
     <row r="20" hidden="1" outlineLevel="2">
       <c r="A20" s="4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="n"/>
@@ -713,7 +713,7 @@
     </row>
     <row r="21" hidden="1" outlineLevel="2">
       <c r="A21" s="4" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6" t="n"/>
@@ -724,7 +724,7 @@
     </row>
     <row r="22" collapsed="1">
       <c r="A22" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
     </row>
     <row r="23" hidden="1" outlineLevel="2">
       <c r="A23" s="4" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="n"/>
@@ -762,7 +762,7 @@
     </row>
     <row r="24" hidden="1" outlineLevel="2">
       <c r="A24" s="4" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="n"/>
@@ -773,7 +773,7 @@
     </row>
     <row r="25" hidden="1" outlineLevel="2">
       <c r="A25" s="4" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6" t="n"/>
@@ -784,7 +784,7 @@
     </row>
     <row r="26" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="n"/>
@@ -795,7 +795,7 @@
     </row>
     <row r="27" hidden="1" outlineLevel="2">
       <c r="A27" s="4" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6" t="n"/>
@@ -806,7 +806,7 @@
     </row>
     <row r="28" hidden="1" outlineLevel="2">
       <c r="A28" s="4" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="n"/>
@@ -817,7 +817,7 @@
     </row>
     <row r="29" hidden="1" outlineLevel="2">
       <c r="A29" s="4" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6" t="n"/>
@@ -828,7 +828,7 @@
     </row>
     <row r="30" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A30" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="n"/>
@@ -839,7 +839,7 @@
     </row>
     <row r="31" hidden="1" outlineLevel="2">
       <c r="A31" s="4" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6" t="n"/>
@@ -850,7 +850,7 @@
     </row>
     <row r="32" hidden="1" outlineLevel="2">
       <c r="A32" s="4" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="n"/>
@@ -861,7 +861,7 @@
     </row>
     <row r="33" hidden="1" outlineLevel="2">
       <c r="A33" s="4" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6" t="n"/>
@@ -872,7 +872,7 @@
     </row>
     <row r="34" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A34" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="n"/>
@@ -883,7 +883,7 @@
     </row>
     <row r="35" hidden="1" outlineLevel="2">
       <c r="A35" s="4" t="n">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6" t="n"/>
@@ -894,7 +894,7 @@
     </row>
     <row r="36" hidden="1" outlineLevel="2">
       <c r="A36" s="4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="n"/>
@@ -905,7 +905,7 @@
     </row>
     <row r="37" hidden="1" outlineLevel="2">
       <c r="A37" s="4" t="n">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6" t="n"/>
@@ -916,7 +916,7 @@
     </row>
     <row r="38" collapsed="1">
       <c r="A38" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     </row>
     <row r="39" hidden="1" outlineLevel="2">
       <c r="A39" s="4" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6" t="n"/>
@@ -954,7 +954,7 @@
     </row>
     <row r="40" hidden="1" outlineLevel="2">
       <c r="A40" s="4" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="n"/>
@@ -965,7 +965,7 @@
     </row>
     <row r="41" hidden="1" outlineLevel="2">
       <c r="A41" s="4" t="n">
-        <v>8.75</v>
+        <v>9.75</v>
       </c>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6" t="n"/>
@@ -976,7 +976,7 @@
     </row>
     <row r="42" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A42" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6" t="n"/>
@@ -987,7 +987,7 @@
     </row>
     <row r="43" hidden="1" outlineLevel="2">
       <c r="A43" s="4" t="n">
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6" t="n"/>
@@ -998,7 +998,7 @@
     </row>
     <row r="44" hidden="1" outlineLevel="2">
       <c r="A44" s="4" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6" t="n"/>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="45" hidden="1" outlineLevel="2">
       <c r="A45" s="4" t="n">
-        <v>9.75</v>
+        <v>10.75</v>
       </c>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6" t="n"/>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="46" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A46" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6" t="n"/>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="47" hidden="1" outlineLevel="2">
       <c r="A47" s="4" t="n">
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6" t="n"/>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="48" hidden="1" outlineLevel="2">
       <c r="A48" s="4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6" t="n"/>
@@ -1053,7 +1053,7 @@
     </row>
     <row r="49" hidden="1" outlineLevel="2">
       <c r="A49" s="4" t="n">
-        <v>10.75</v>
+        <v>11.75</v>
       </c>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6" t="n"/>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="50" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A50" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6" t="n"/>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="51" hidden="1" outlineLevel="2">
       <c r="A51" s="4" t="n">
-        <v>11.25</v>
+        <v>12.25</v>
       </c>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6" t="n"/>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="52" hidden="1" outlineLevel="2">
       <c r="A52" s="4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6" t="n"/>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="53" hidden="1" outlineLevel="2">
       <c r="A53" s="4" t="n">
-        <v>11.75</v>
+        <v>12.75</v>
       </c>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6" t="n"/>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="54" collapsed="1">
       <c r="A54" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="55" hidden="1" outlineLevel="2">
       <c r="A55" s="4" t="n">
-        <v>12.25</v>
+        <v>13.25</v>
       </c>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6" t="n"/>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="56" hidden="1" outlineLevel="2">
       <c r="A56" s="4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6" t="n"/>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="57" hidden="1" outlineLevel="2">
       <c r="A57" s="4" t="n">
-        <v>12.75</v>
+        <v>13.75</v>
       </c>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6" t="n"/>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="58" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A58" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6" t="n"/>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="59" hidden="1" outlineLevel="2">
       <c r="A59" s="4" t="n">
-        <v>13.25</v>
+        <v>14.25</v>
       </c>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6" t="n"/>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="60" hidden="1" outlineLevel="2">
       <c r="A60" s="4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6" t="n"/>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="61" hidden="1" outlineLevel="2">
       <c r="A61" s="4" t="n">
-        <v>13.75</v>
+        <v>14.75</v>
       </c>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6" t="n"/>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="62" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A62" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6" t="n"/>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="63" hidden="1" outlineLevel="2">
       <c r="A63" s="4" t="n">
-        <v>14.25</v>
+        <v>15.25</v>
       </c>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6" t="n"/>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="64" hidden="1" outlineLevel="2">
       <c r="A64" s="4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6" t="n"/>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="65" hidden="1" outlineLevel="2">
       <c r="A65" s="4" t="n">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6" t="n"/>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="66" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A66" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6" t="n"/>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="67" hidden="1" outlineLevel="2">
       <c r="A67" s="4" t="n">
-        <v>15.25</v>
+        <v>16.25</v>
       </c>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6" t="n"/>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="68" hidden="1" outlineLevel="2">
       <c r="A68" s="4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6" t="n"/>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="69" hidden="1" outlineLevel="2">
       <c r="A69" s="4" t="n">
-        <v>15.75</v>
+        <v>16.75</v>
       </c>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6" t="n"/>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="70" collapsed="1">
       <c r="A70" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="71" hidden="1" outlineLevel="2">
       <c r="A71" s="4" t="n">
-        <v>16.25</v>
+        <v>17.25</v>
       </c>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6" t="n"/>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="72" hidden="1" outlineLevel="2">
       <c r="A72" s="4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6" t="n"/>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="73" hidden="1" outlineLevel="2">
       <c r="A73" s="4" t="n">
-        <v>16.75</v>
+        <v>17.75</v>
       </c>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6" t="n"/>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="74" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A74" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6" t="n"/>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="75" hidden="1" outlineLevel="2">
       <c r="A75" s="4" t="n">
-        <v>17.25</v>
+        <v>18.25</v>
       </c>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6" t="n"/>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="76" hidden="1" outlineLevel="2">
       <c r="A76" s="4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6" t="n"/>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="77" hidden="1" outlineLevel="2">
       <c r="A77" s="4" t="n">
-        <v>17.75</v>
+        <v>18.75</v>
       </c>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6" t="n"/>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="78" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A78" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6" t="n"/>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="79" hidden="1" outlineLevel="2">
       <c r="A79" s="4" t="n">
-        <v>18.25</v>
+        <v>19.25</v>
       </c>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6" t="n"/>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="80" hidden="1" outlineLevel="2">
       <c r="A80" s="4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6" t="n"/>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="81" hidden="1" outlineLevel="2">
       <c r="A81" s="4" t="n">
-        <v>18.75</v>
+        <v>19.75</v>
       </c>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6" t="n"/>
@@ -1448,7 +1448,7 @@
     </row>
     <row r="82" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A82" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6" t="n"/>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="83" hidden="1" outlineLevel="2">
       <c r="A83" s="4" t="n">
-        <v>19.25</v>
+        <v>20.25</v>
       </c>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6" t="n"/>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="84" hidden="1" outlineLevel="2">
       <c r="A84" s="4" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6" t="n"/>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="85" hidden="1" outlineLevel="2">
       <c r="A85" s="4" t="n">
-        <v>19.75</v>
+        <v>20.75</v>
       </c>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6" t="n"/>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="86" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A86" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6" t="n"/>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="87" hidden="1" outlineLevel="2">
       <c r="A87" s="4" t="n">
-        <v>20.25</v>
+        <v>21.25</v>
       </c>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6" t="n"/>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="88" hidden="1" outlineLevel="2">
       <c r="A88" s="4" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6" t="n"/>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="89" hidden="1" outlineLevel="2">
       <c r="A89" s="4" t="n">
-        <v>20.75</v>
+        <v>21.75</v>
       </c>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6" t="n"/>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="90" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A90" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6" t="n"/>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="91" hidden="1" outlineLevel="2">
       <c r="A91" s="4" t="n">
-        <v>21.25</v>
+        <v>22.25</v>
       </c>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6" t="n"/>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="92" hidden="1" outlineLevel="2">
       <c r="A92" s="4" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6" t="n"/>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="93" hidden="1" outlineLevel="2">
       <c r="A93" s="4" t="n">
-        <v>21.75</v>
+        <v>22.75</v>
       </c>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6" t="n"/>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="94" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A94" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6" t="n"/>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="95" hidden="1" outlineLevel="2">
       <c r="A95" s="4" t="n">
-        <v>22.25</v>
+        <v>23.25</v>
       </c>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6" t="n"/>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="96" hidden="1" outlineLevel="2">
       <c r="A96" s="4" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6" t="n"/>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="97" hidden="1" outlineLevel="2">
       <c r="A97" s="4" t="n">
-        <v>22.75</v>
+        <v>23.75</v>
       </c>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6" t="n"/>
@@ -1624,7 +1624,7 @@
     </row>
     <row r="98" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A98" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6" t="n"/>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="99" hidden="1" outlineLevel="2">
       <c r="A99" s="4" t="n">
-        <v>23.25</v>
+        <v>24.25</v>
       </c>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6" t="n"/>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="100" hidden="1" outlineLevel="2">
       <c r="A100" s="4" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6" t="n"/>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="101" hidden="1" outlineLevel="2">
       <c r="A101" s="4" t="n">
-        <v>23.75</v>
+        <v>24.75</v>
       </c>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6" t="n"/>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="102" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A102" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6" t="n"/>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="103" hidden="1" outlineLevel="2">
       <c r="A103" s="4" t="n">
-        <v>24.25</v>
+        <v>25.25</v>
       </c>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6" t="n"/>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="104" hidden="1" outlineLevel="2">
       <c r="A104" s="4" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6" t="n"/>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="105" hidden="1" outlineLevel="2">
       <c r="A105" s="4" t="n">
-        <v>24.75</v>
+        <v>25.75</v>
       </c>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6" t="n"/>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="106" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A106" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6" t="n"/>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="107" hidden="1" outlineLevel="2">
       <c r="A107" s="4" t="n">
-        <v>25.25</v>
+        <v>26.25</v>
       </c>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6" t="n"/>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="108" hidden="1" outlineLevel="2">
       <c r="A108" s="4" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6" t="n"/>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="109" hidden="1" outlineLevel="2">
       <c r="A109" s="4" t="n">
-        <v>25.75</v>
+        <v>26.75</v>
       </c>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6" t="n"/>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="110" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A110" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6" t="n"/>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="111" hidden="1" outlineLevel="2">
       <c r="A111" s="4" t="n">
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6" t="n"/>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="112" hidden="1" outlineLevel="2">
       <c r="A112" s="4" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6" t="n"/>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="113" hidden="1" outlineLevel="2">
       <c r="A113" s="4" t="n">
-        <v>26.75</v>
+        <v>27.75</v>
       </c>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6" t="n"/>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="114" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A114" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6" t="n"/>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="115" hidden="1" outlineLevel="2">
       <c r="A115" s="4" t="n">
-        <v>27.25</v>
+        <v>28.25</v>
       </c>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6" t="n"/>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="116" hidden="1" outlineLevel="2">
       <c r="A116" s="4" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6" t="n"/>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="117" hidden="1" outlineLevel="2">
       <c r="A117" s="4" t="n">
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6" t="n"/>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="118" collapsed="1">
       <c r="A118" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="119" hidden="1" outlineLevel="2">
       <c r="A119" s="4" t="n">
-        <v>28.25</v>
+        <v>29.25</v>
       </c>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6" t="n"/>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="120" hidden="1" outlineLevel="2">
       <c r="A120" s="4" t="n">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6" t="n"/>
@@ -1893,7 +1893,7 @@
     </row>
     <row r="121" hidden="1" outlineLevel="2">
       <c r="A121" s="4" t="n">
-        <v>28.75</v>
+        <v>29.75</v>
       </c>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6" t="n"/>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="122" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A122" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6" t="n"/>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="123" hidden="1" outlineLevel="2">
       <c r="A123" s="4" t="n">
-        <v>29.25</v>
+        <v>30.25</v>
       </c>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6" t="n"/>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="124" hidden="1" outlineLevel="2">
       <c r="A124" s="4" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6" t="n"/>
@@ -1937,7 +1937,7 @@
     </row>
     <row r="125" hidden="1" outlineLevel="2">
       <c r="A125" s="4" t="n">
-        <v>29.75</v>
+        <v>30.75</v>
       </c>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6" t="n"/>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="126" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A126" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6" t="n"/>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="127" hidden="1" outlineLevel="2">
       <c r="A127" s="4" t="n">
-        <v>30.25</v>
+        <v>31.25</v>
       </c>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6" t="n"/>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="128" hidden="1" outlineLevel="2">
       <c r="A128" s="4" t="n">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6" t="n"/>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="129" hidden="1" outlineLevel="2">
       <c r="A129" s="4" t="n">
-        <v>30.75</v>
+        <v>31.75</v>
       </c>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6" t="n"/>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="130" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A130" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6" t="n"/>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="131" hidden="1" outlineLevel="2">
       <c r="A131" s="4" t="n">
-        <v>31.25</v>
+        <v>32.25</v>
       </c>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6" t="n"/>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="132" hidden="1" outlineLevel="2">
       <c r="A132" s="4" t="n">
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6" t="n"/>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="133" hidden="1" outlineLevel="2">
       <c r="A133" s="4" t="n">
-        <v>31.75</v>
+        <v>32.75</v>
       </c>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6" t="n"/>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="134" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A134" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6" t="n"/>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="135" hidden="1" outlineLevel="2">
       <c r="A135" s="4" t="n">
-        <v>32.25</v>
+        <v>33.25</v>
       </c>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6" t="n"/>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="136" hidden="1" outlineLevel="2">
       <c r="A136" s="4" t="n">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6" t="n"/>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="137" hidden="1" outlineLevel="2">
       <c r="A137" s="4" t="n">
-        <v>32.75</v>
+        <v>33.75</v>
       </c>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6" t="n"/>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="138" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A138" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6" t="n"/>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="139" hidden="1" outlineLevel="2">
       <c r="A139" s="4" t="n">
-        <v>33.25</v>
+        <v>34.25</v>
       </c>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6" t="n"/>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="140" hidden="1" outlineLevel="2">
       <c r="A140" s="4" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6" t="n"/>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="141" hidden="1" outlineLevel="2">
       <c r="A141" s="4" t="n">
-        <v>33.75</v>
+        <v>34.75</v>
       </c>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6" t="n"/>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="142" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A142" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6" t="n"/>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="143" hidden="1" outlineLevel="2">
       <c r="A143" s="4" t="n">
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6" t="n"/>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="144" hidden="1" outlineLevel="2">
       <c r="A144" s="4" t="n">
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6" t="n"/>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="145" hidden="1" outlineLevel="2">
       <c r="A145" s="4" t="n">
-        <v>34.75</v>
+        <v>35.75</v>
       </c>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6" t="n"/>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="146" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A146" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6" t="n"/>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="147" hidden="1" outlineLevel="2">
       <c r="A147" s="4" t="n">
-        <v>35.25</v>
+        <v>36.25</v>
       </c>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6" t="n"/>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="148" hidden="1" outlineLevel="2">
       <c r="A148" s="4" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6" t="n"/>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="149" hidden="1" outlineLevel="2">
       <c r="A149" s="4" t="n">
-        <v>35.75</v>
+        <v>36.75</v>
       </c>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6" t="n"/>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="150" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A150" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6" t="n"/>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="151" hidden="1" outlineLevel="2">
       <c r="A151" s="4" t="n">
-        <v>36.25</v>
+        <v>37.25</v>
       </c>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6" t="n"/>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="152" hidden="1" outlineLevel="2">
       <c r="A152" s="4" t="n">
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6" t="n"/>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="153" hidden="1" outlineLevel="2">
       <c r="A153" s="4" t="n">
-        <v>36.75</v>
+        <v>37.75</v>
       </c>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6" t="n"/>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="154" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A154" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6" t="n"/>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="155" hidden="1" outlineLevel="2">
       <c r="A155" s="4" t="n">
-        <v>37.25</v>
+        <v>38.25</v>
       </c>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6" t="n"/>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="156" hidden="1" outlineLevel="2">
       <c r="A156" s="4" t="n">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6" t="n"/>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="157" hidden="1" outlineLevel="2">
       <c r="A157" s="4" t="n">
-        <v>37.75</v>
+        <v>38.75</v>
       </c>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6" t="n"/>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="158" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A158" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6" t="n"/>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="159" hidden="1" outlineLevel="2">
       <c r="A159" s="4" t="n">
-        <v>38.25</v>
+        <v>39.25</v>
       </c>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6" t="n"/>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="160" hidden="1" outlineLevel="2">
       <c r="A160" s="4" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6" t="n"/>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="161" hidden="1" outlineLevel="2">
       <c r="A161" s="4" t="n">
-        <v>38.75</v>
+        <v>39.75</v>
       </c>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6" t="n"/>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="162" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A162" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6" t="n"/>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="163" hidden="1" outlineLevel="2">
       <c r="A163" s="4" t="n">
-        <v>39.25</v>
+        <v>40.25</v>
       </c>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6" t="n"/>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="164" hidden="1" outlineLevel="2">
       <c r="A164" s="4" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6" t="n"/>
@@ -2377,7 +2377,7 @@
     </row>
     <row r="165" hidden="1" outlineLevel="2">
       <c r="A165" s="4" t="n">
-        <v>39.75</v>
+        <v>40.75</v>
       </c>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6" t="n"/>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="166" collapsed="1">
       <c r="A166" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="167" hidden="1" outlineLevel="2">
       <c r="A167" s="4" t="n">
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6" t="n"/>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="168" hidden="1" outlineLevel="2">
       <c r="A168" s="4" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6" t="n"/>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="169" hidden="1" outlineLevel="2">
       <c r="A169" s="4" t="n">
-        <v>40.75</v>
+        <v>41.75</v>
       </c>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6" t="n"/>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="170" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A170" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6" t="n"/>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="171" hidden="1" outlineLevel="2">
       <c r="A171" s="4" t="n">
-        <v>41.25</v>
+        <v>42.25</v>
       </c>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6" t="n"/>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="172" hidden="1" outlineLevel="2">
       <c r="A172" s="4" t="n">
-        <v>41.5</v>
+        <v>42.5</v>
       </c>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6" t="n"/>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="173" hidden="1" outlineLevel="2">
       <c r="A173" s="4" t="n">
-        <v>41.75</v>
+        <v>42.75</v>
       </c>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6" t="n"/>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="174" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A174" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6" t="n"/>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="175" hidden="1" outlineLevel="2">
       <c r="A175" s="4" t="n">
-        <v>42.25</v>
+        <v>43.25</v>
       </c>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6" t="n"/>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="176" hidden="1" outlineLevel="2">
       <c r="A176" s="4" t="n">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6" t="n"/>
@@ -2525,7 +2525,7 @@
     </row>
     <row r="177" hidden="1" outlineLevel="2">
       <c r="A177" s="4" t="n">
-        <v>42.75</v>
+        <v>43.75</v>
       </c>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6" t="n"/>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="178" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A178" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6" t="n"/>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="179" hidden="1" outlineLevel="2">
       <c r="A179" s="4" t="n">
-        <v>43.25</v>
+        <v>44.25</v>
       </c>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6" t="n"/>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="180" hidden="1" outlineLevel="2">
       <c r="A180" s="4" t="n">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6" t="n"/>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="181" hidden="1" outlineLevel="2">
       <c r="A181" s="4" t="n">
-        <v>43.75</v>
+        <v>44.75</v>
       </c>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6" t="n"/>
@@ -2580,7 +2580,7 @@
     </row>
     <row r="182" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A182" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6" t="n"/>
@@ -2591,7 +2591,7 @@
     </row>
     <row r="183" hidden="1" outlineLevel="2">
       <c r="A183" s="4" t="n">
-        <v>44.25</v>
+        <v>45.25</v>
       </c>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6" t="n"/>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="184" hidden="1" outlineLevel="2">
       <c r="A184" s="4" t="n">
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6" t="n"/>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="185" hidden="1" outlineLevel="2">
       <c r="A185" s="4" t="n">
-        <v>44.75</v>
+        <v>45.75</v>
       </c>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6" t="n"/>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="186" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A186" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6" t="n"/>
@@ -2635,7 +2635,7 @@
     </row>
     <row r="187" hidden="1" outlineLevel="2">
       <c r="A187" s="4" t="n">
-        <v>45.25</v>
+        <v>46.25</v>
       </c>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6" t="n"/>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="188" hidden="1" outlineLevel="2">
       <c r="A188" s="4" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6" t="n"/>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="189" hidden="1" outlineLevel="2">
       <c r="A189" s="4" t="n">
-        <v>45.75</v>
+        <v>46.75</v>
       </c>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6" t="n"/>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="190" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A190" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6" t="n"/>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="191" hidden="1" outlineLevel="2">
       <c r="A191" s="4" t="n">
-        <v>46.25</v>
+        <v>47.25</v>
       </c>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6" t="n"/>
@@ -2690,7 +2690,7 @@
     </row>
     <row r="192" hidden="1" outlineLevel="2">
       <c r="A192" s="4" t="n">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6" t="n"/>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="193" hidden="1" outlineLevel="2">
       <c r="A193" s="4" t="n">
-        <v>46.75</v>
+        <v>47.75</v>
       </c>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6" t="n"/>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="194" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A194" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6" t="n"/>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="195" hidden="1" outlineLevel="2">
       <c r="A195" s="4" t="n">
-        <v>47.25</v>
+        <v>48.25</v>
       </c>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6" t="n"/>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="196" hidden="1" outlineLevel="2">
       <c r="A196" s="4" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6" t="n"/>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="197" hidden="1" outlineLevel="2">
       <c r="A197" s="4" t="n">
-        <v>47.75</v>
+        <v>48.75</v>
       </c>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6" t="n"/>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="198" collapsed="1">
       <c r="A198" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="199" hidden="1" outlineLevel="2">
       <c r="A199" s="4" t="n">
-        <v>48.25</v>
+        <v>49.25</v>
       </c>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6" t="n"/>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="200" hidden="1" outlineLevel="2">
       <c r="A200" s="4" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6" t="n"/>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="201" hidden="1" outlineLevel="2">
       <c r="A201" s="4" t="n">
-        <v>48.75</v>
+        <v>49.75</v>
       </c>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6" t="n"/>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="202" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A202" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6" t="n"/>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="203" hidden="1" outlineLevel="2">
       <c r="A203" s="4" t="n">
-        <v>49.25</v>
+        <v>50.25</v>
       </c>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6" t="n"/>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="204" hidden="1" outlineLevel="2">
       <c r="A204" s="4" t="n">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6" t="n"/>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="205" hidden="1" outlineLevel="2">
       <c r="A205" s="4" t="n">
-        <v>49.75</v>
+        <v>50.75</v>
       </c>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6" t="n"/>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="206" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A206" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6" t="n"/>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="207" hidden="1" outlineLevel="2">
       <c r="A207" s="4" t="n">
-        <v>50.25</v>
+        <v>51.25</v>
       </c>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6" t="n"/>
@@ -2882,7 +2882,7 @@
     </row>
     <row r="208" hidden="1" outlineLevel="2">
       <c r="A208" s="4" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6" t="n"/>
@@ -2893,7 +2893,7 @@
     </row>
     <row r="209" hidden="1" outlineLevel="2">
       <c r="A209" s="4" t="n">
-        <v>50.75</v>
+        <v>51.75</v>
       </c>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6" t="n"/>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="210" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A210" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6" t="n"/>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="211" hidden="1" outlineLevel="2">
       <c r="A211" s="4" t="n">
-        <v>51.25</v>
+        <v>52.25</v>
       </c>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6" t="n"/>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="212" hidden="1" outlineLevel="2">
       <c r="A212" s="4" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6" t="n"/>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="213" hidden="1" outlineLevel="2">
       <c r="A213" s="4" t="n">
-        <v>51.75</v>
+        <v>52.75</v>
       </c>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6" t="n"/>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="214" collapsed="1">
       <c r="A214" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="215" hidden="1" outlineLevel="2">
       <c r="A215" s="4" t="n">
-        <v>52.25</v>
+        <v>53.25</v>
       </c>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6" t="n"/>
@@ -2986,7 +2986,7 @@
     </row>
     <row r="216" hidden="1" outlineLevel="2">
       <c r="A216" s="4" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6" t="n"/>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="217" hidden="1" outlineLevel="2">
       <c r="A217" s="4" t="n">
-        <v>52.75</v>
+        <v>53.75</v>
       </c>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6" t="n"/>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="218" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A218" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6" t="n"/>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="219" hidden="1" outlineLevel="2">
       <c r="A219" s="4" t="n">
-        <v>53.25</v>
+        <v>54.25</v>
       </c>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6" t="n"/>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="220" hidden="1" outlineLevel="2">
       <c r="A220" s="4" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6" t="n"/>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="221" hidden="1" outlineLevel="2">
       <c r="A221" s="4" t="n">
-        <v>53.75</v>
+        <v>54.75</v>
       </c>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6" t="n"/>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="222" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A222" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6" t="n"/>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="223" hidden="1" outlineLevel="2">
       <c r="A223" s="4" t="n">
-        <v>54.25</v>
+        <v>55.25</v>
       </c>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6" t="n"/>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="224" hidden="1" outlineLevel="2">
       <c r="A224" s="4" t="n">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6" t="n"/>
@@ -3085,7 +3085,7 @@
     </row>
     <row r="225" hidden="1" outlineLevel="2">
       <c r="A225" s="4" t="n">
-        <v>54.75</v>
+        <v>55.75</v>
       </c>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6" t="n"/>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="226" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A226" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6" t="n"/>
@@ -3107,7 +3107,7 @@
     </row>
     <row r="227" hidden="1" outlineLevel="2">
       <c r="A227" s="4" t="n">
-        <v>55.25</v>
+        <v>56.25</v>
       </c>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6" t="n"/>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="228" hidden="1" outlineLevel="2">
       <c r="A228" s="4" t="n">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6" t="n"/>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="229" hidden="1" outlineLevel="2">
       <c r="A229" s="4" t="n">
-        <v>55.75</v>
+        <v>56.75</v>
       </c>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6" t="n"/>
@@ -3140,7 +3140,7 @@
     </row>
     <row r="230" collapsed="1">
       <c r="A230" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="231" hidden="1" outlineLevel="2">
       <c r="A231" s="4" t="n">
-        <v>56.25</v>
+        <v>57.25</v>
       </c>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6" t="n"/>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="232" hidden="1" outlineLevel="2">
       <c r="A232" s="4" t="n">
-        <v>56.5</v>
+        <v>57.5</v>
       </c>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6" t="n"/>
@@ -3189,7 +3189,7 @@
     </row>
     <row r="233" hidden="1" outlineLevel="2">
       <c r="A233" s="4" t="n">
-        <v>56.75</v>
+        <v>57.75</v>
       </c>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6" t="n"/>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="234" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A234" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6" t="n"/>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="235" hidden="1" outlineLevel="2">
       <c r="A235" s="4" t="n">
-        <v>57.25</v>
+        <v>58.25</v>
       </c>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6" t="n"/>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="236" hidden="1" outlineLevel="2">
       <c r="A236" s="4" t="n">
-        <v>57.5</v>
+        <v>58.5</v>
       </c>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6" t="n"/>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="237" hidden="1" outlineLevel="2">
       <c r="A237" s="4" t="n">
-        <v>57.75</v>
+        <v>58.75</v>
       </c>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6" t="n"/>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="238" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A238" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6" t="n"/>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="239" hidden="1" outlineLevel="2">
       <c r="A239" s="4" t="n">
-        <v>58.25</v>
+        <v>59.25</v>
       </c>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6" t="n"/>
@@ -3266,7 +3266,7 @@
     </row>
     <row r="240" hidden="1" outlineLevel="2">
       <c r="A240" s="4" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6" t="n"/>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="241" hidden="1" outlineLevel="2">
       <c r="A241" s="4" t="n">
-        <v>58.75</v>
+        <v>59.75</v>
       </c>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6" t="n"/>
@@ -3288,7 +3288,7 @@
     </row>
     <row r="242" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A242" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6" t="n"/>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="243" hidden="1" outlineLevel="2">
       <c r="A243" s="4" t="n">
-        <v>59.25</v>
+        <v>60.25</v>
       </c>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6" t="n"/>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="244" hidden="1" outlineLevel="2">
       <c r="A244" s="4" t="n">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6" t="n"/>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="245" hidden="1" outlineLevel="2">
       <c r="A245" s="4" t="n">
-        <v>59.75</v>
+        <v>60.75</v>
       </c>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6" t="n"/>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="246" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A246" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6" t="n"/>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="247" hidden="1" outlineLevel="2">
       <c r="A247" s="4" t="n">
-        <v>60.25</v>
+        <v>61.25</v>
       </c>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6" t="n"/>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="248" hidden="1" outlineLevel="2">
       <c r="A248" s="4" t="n">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6" t="n"/>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="249" hidden="1" outlineLevel="2">
       <c r="A249" s="4" t="n">
-        <v>60.75</v>
+        <v>61.75</v>
       </c>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6" t="n"/>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="250" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A250" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6" t="n"/>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="251" hidden="1" outlineLevel="2">
       <c r="A251" s="4" t="n">
-        <v>61.25</v>
+        <v>62.25</v>
       </c>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6" t="n"/>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="252" hidden="1" outlineLevel="2">
       <c r="A252" s="4" t="n">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6" t="n"/>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="253" hidden="1" outlineLevel="2">
       <c r="A253" s="4" t="n">
-        <v>61.75</v>
+        <v>62.75</v>
       </c>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6" t="n"/>
@@ -3420,7 +3420,7 @@
     </row>
     <row r="254" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A254" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6" t="n"/>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="255" hidden="1" outlineLevel="2">
       <c r="A255" s="4" t="n">
-        <v>62.25</v>
+        <v>63.25</v>
       </c>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6" t="n"/>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="256" hidden="1" outlineLevel="2">
       <c r="A256" s="4" t="n">
-        <v>62.5</v>
+        <v>63.5</v>
       </c>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6" t="n"/>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="257" hidden="1" outlineLevel="2">
       <c r="A257" s="4" t="n">
-        <v>62.75</v>
+        <v>63.75</v>
       </c>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6" t="n"/>
@@ -3464,7 +3464,7 @@
     </row>
     <row r="258" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A258" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6" t="n"/>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="259" hidden="1" outlineLevel="2">
       <c r="A259" s="4" t="n">
-        <v>63.25</v>
+        <v>64.25</v>
       </c>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6" t="n"/>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="260" hidden="1" outlineLevel="2">
       <c r="A260" s="4" t="n">
-        <v>63.5</v>
+        <v>64.5</v>
       </c>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6" t="n"/>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="261" hidden="1" outlineLevel="2">
       <c r="A261" s="4" t="n">
-        <v>63.75</v>
+        <v>64.75</v>
       </c>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6" t="n"/>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="262" collapsed="1">
       <c r="A262" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="263" hidden="1" outlineLevel="2">
       <c r="A263" s="4" t="n">
-        <v>64.25</v>
+        <v>65.25</v>
       </c>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6" t="n"/>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="264" hidden="1" outlineLevel="2">
       <c r="A264" s="4" t="n">
-        <v>64.5</v>
+        <v>65.5</v>
       </c>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6" t="n"/>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="265" hidden="1" outlineLevel="2">
       <c r="A265" s="4" t="n">
-        <v>64.75</v>
+        <v>65.75</v>
       </c>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6" t="n"/>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="266" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A266" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6" t="n"/>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="267" hidden="1" outlineLevel="2">
       <c r="A267" s="4" t="n">
-        <v>65.25</v>
+        <v>66.25</v>
       </c>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6" t="n"/>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="268" hidden="1" outlineLevel="2">
       <c r="A268" s="4" t="n">
-        <v>65.5</v>
+        <v>66.5</v>
       </c>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6" t="n"/>
@@ -3601,7 +3601,7 @@
     </row>
     <row r="269" hidden="1" outlineLevel="2">
       <c r="A269" s="4" t="n">
-        <v>65.75</v>
+        <v>66.75</v>
       </c>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6" t="n"/>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="270" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A270" s="4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6" t="n"/>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="271" hidden="1" outlineLevel="2">
       <c r="A271" s="4" t="n">
-        <v>66.25</v>
+        <v>67.25</v>
       </c>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6" t="n"/>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="272" hidden="1" outlineLevel="2">
       <c r="A272" s="4" t="n">
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6" t="n"/>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="273" hidden="1" outlineLevel="2">
       <c r="A273" s="4" t="n">
-        <v>66.75</v>
+        <v>67.75</v>
       </c>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6" t="n"/>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="274" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A274" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6" t="n"/>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="275" hidden="1" outlineLevel="2">
       <c r="A275" s="4" t="n">
-        <v>67.25</v>
+        <v>68.25</v>
       </c>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6" t="n"/>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="276" hidden="1" outlineLevel="2">
       <c r="A276" s="4" t="n">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6" t="n"/>
@@ -3689,7 +3689,7 @@
     </row>
     <row r="277" hidden="1" outlineLevel="2">
       <c r="A277" s="4" t="n">
-        <v>67.75</v>
+        <v>68.75</v>
       </c>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6" t="n"/>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="278" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A278" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6" t="n"/>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="279" hidden="1" outlineLevel="2">
       <c r="A279" s="4" t="n">
-        <v>68.25</v>
+        <v>69.25</v>
       </c>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6" t="n"/>
@@ -3722,7 +3722,7 @@
     </row>
     <row r="280" hidden="1" outlineLevel="2">
       <c r="A280" s="4" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6" t="n"/>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="281" hidden="1" outlineLevel="2">
       <c r="A281" s="4" t="n">
-        <v>68.75</v>
+        <v>69.75</v>
       </c>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6" t="n"/>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="282" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A282" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6" t="n"/>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="283" hidden="1" outlineLevel="2">
       <c r="A283" s="4" t="n">
-        <v>69.25</v>
+        <v>70.25</v>
       </c>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6" t="n"/>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="284" hidden="1" outlineLevel="2">
       <c r="A284" s="4" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6" t="n"/>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="285" hidden="1" outlineLevel="2">
       <c r="A285" s="4" t="n">
-        <v>69.75</v>
+        <v>70.75</v>
       </c>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6" t="n"/>
@@ -3788,7 +3788,7 @@
     </row>
     <row r="286" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A286" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6" t="n"/>
@@ -3799,7 +3799,7 @@
     </row>
     <row r="287" hidden="1" outlineLevel="2">
       <c r="A287" s="4" t="n">
-        <v>70.25</v>
+        <v>71.25</v>
       </c>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6" t="n"/>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="288" hidden="1" outlineLevel="2">
       <c r="A288" s="4" t="n">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6" t="n"/>
@@ -3821,7 +3821,7 @@
     </row>
     <row r="289" hidden="1" outlineLevel="2">
       <c r="A289" s="4" t="n">
-        <v>70.75</v>
+        <v>71.75</v>
       </c>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6" t="n"/>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="290" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A290" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6" t="n"/>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="291" hidden="1" outlineLevel="2">
       <c r="A291" s="4" t="n">
-        <v>71.25</v>
+        <v>72.25</v>
       </c>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6" t="n"/>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="292" hidden="1" outlineLevel="2">
       <c r="A292" s="4" t="n">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6" t="n"/>
@@ -3865,7 +3865,7 @@
     </row>
     <row r="293" hidden="1" outlineLevel="2">
       <c r="A293" s="4" t="n">
-        <v>71.75</v>
+        <v>72.75</v>
       </c>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6" t="n"/>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="294" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A294" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6" t="n"/>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="295" hidden="1" outlineLevel="2">
       <c r="A295" s="4" t="n">
-        <v>72.25</v>
+        <v>73.25</v>
       </c>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6" t="n"/>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="296" hidden="1" outlineLevel="2">
       <c r="A296" s="4" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6" t="n"/>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="297" hidden="1" outlineLevel="2">
       <c r="A297" s="4" t="n">
-        <v>72.75</v>
+        <v>73.75</v>
       </c>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6" t="n"/>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="298" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A298" s="4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6" t="n"/>
@@ -3931,7 +3931,7 @@
     </row>
     <row r="299" hidden="1" outlineLevel="2">
       <c r="A299" s="4" t="n">
-        <v>73.25</v>
+        <v>74.25</v>
       </c>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6" t="n"/>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="300" hidden="1" outlineLevel="2">
       <c r="A300" s="4" t="n">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6" t="n"/>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="301" hidden="1" outlineLevel="2">
       <c r="A301" s="4" t="n">
-        <v>73.75</v>
+        <v>74.75</v>
       </c>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6" t="n"/>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="302" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A302" s="4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6" t="n"/>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="303" hidden="1" outlineLevel="2">
       <c r="A303" s="4" t="n">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6" t="n"/>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="304" hidden="1" outlineLevel="2">
       <c r="A304" s="4" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6" t="n"/>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="305" hidden="1" outlineLevel="2">
       <c r="A305" s="4" t="n">
-        <v>74.75</v>
+        <v>75.75</v>
       </c>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6" t="n"/>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="306" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A306" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6" t="n"/>
@@ -4019,7 +4019,7 @@
     </row>
     <row r="307" hidden="1" outlineLevel="2">
       <c r="A307" s="4" t="n">
-        <v>75.25</v>
+        <v>76.25</v>
       </c>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6" t="n"/>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="308" hidden="1" outlineLevel="2">
       <c r="A308" s="4" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6" t="n"/>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="309" hidden="1" outlineLevel="2">
       <c r="A309" s="4" t="n">
-        <v>75.75</v>
+        <v>76.75</v>
       </c>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6" t="n"/>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="310" collapsed="1">
       <c r="A310" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B310" s="5" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="311" hidden="1" outlineLevel="2">
       <c r="A311" s="4" t="n">
-        <v>76.25</v>
+        <v>77.25</v>
       </c>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6" t="n"/>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="312" hidden="1" outlineLevel="2">
       <c r="A312" s="4" t="n">
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6" t="n"/>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="313" hidden="1" outlineLevel="2">
       <c r="A313" s="4" t="n">
-        <v>76.75</v>
+        <v>77.75</v>
       </c>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6" t="n"/>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="314" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A314" s="4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6" t="n"/>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="315" hidden="1" outlineLevel="2">
       <c r="A315" s="4" t="n">
-        <v>77.25</v>
+        <v>78.25</v>
       </c>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6" t="n"/>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="316" hidden="1" outlineLevel="2">
       <c r="A316" s="4" t="n">
-        <v>77.5</v>
+        <v>78.5</v>
       </c>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6" t="n"/>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="317" hidden="1" outlineLevel="2">
       <c r="A317" s="4" t="n">
-        <v>77.75</v>
+        <v>78.75</v>
       </c>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6" t="n"/>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="318" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A318" s="4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6" t="n"/>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="319" hidden="1" outlineLevel="2">
       <c r="A319" s="4" t="n">
-        <v>78.25</v>
+        <v>79.25</v>
       </c>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6" t="n"/>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="320" hidden="1" outlineLevel="2">
       <c r="A320" s="4" t="n">
-        <v>78.5</v>
+        <v>79.5</v>
       </c>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6" t="n"/>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="321" hidden="1" outlineLevel="2">
       <c r="A321" s="4" t="n">
-        <v>78.75</v>
+        <v>79.75</v>
       </c>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6" t="n"/>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="322" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A322" s="4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6" t="n"/>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="323" hidden="1" outlineLevel="2">
       <c r="A323" s="4" t="n">
-        <v>79.25</v>
+        <v>80.25</v>
       </c>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6" t="n"/>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="324" hidden="1" outlineLevel="2">
       <c r="A324" s="4" t="n">
-        <v>79.5</v>
+        <v>80.5</v>
       </c>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6" t="n"/>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="325" hidden="1" outlineLevel="2">
       <c r="A325" s="4" t="n">
-        <v>79.75</v>
+        <v>80.75</v>
       </c>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6" t="n"/>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="326" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A326" s="4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6" t="n"/>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="327" hidden="1" outlineLevel="2">
       <c r="A327" s="4" t="n">
-        <v>80.25</v>
+        <v>81.25</v>
       </c>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6" t="n"/>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="328" hidden="1" outlineLevel="2">
       <c r="A328" s="4" t="n">
-        <v>80.5</v>
+        <v>81.5</v>
       </c>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6" t="n"/>
@@ -4277,7 +4277,7 @@
     </row>
     <row r="329" hidden="1" outlineLevel="2">
       <c r="A329" s="4" t="n">
-        <v>80.75</v>
+        <v>81.75</v>
       </c>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6" t="n"/>
@@ -4288,7 +4288,7 @@
     </row>
     <row r="330" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A330" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6" t="n"/>
@@ -4299,7 +4299,7 @@
     </row>
     <row r="331" hidden="1" outlineLevel="2">
       <c r="A331" s="4" t="n">
-        <v>81.25</v>
+        <v>82.25</v>
       </c>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6" t="n"/>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="332" hidden="1" outlineLevel="2">
       <c r="A332" s="4" t="n">
-        <v>81.5</v>
+        <v>82.5</v>
       </c>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6" t="n"/>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="333" hidden="1" outlineLevel="2">
       <c r="A333" s="4" t="n">
-        <v>81.75</v>
+        <v>82.75</v>
       </c>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6" t="n"/>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="334" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A334" s="4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6" t="n"/>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="335" hidden="1" outlineLevel="2">
       <c r="A335" s="4" t="n">
-        <v>82.25</v>
+        <v>83.25</v>
       </c>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6" t="n"/>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="336" hidden="1" outlineLevel="2">
       <c r="A336" s="4" t="n">
-        <v>82.5</v>
+        <v>83.5</v>
       </c>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6" t="n"/>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="337" hidden="1" outlineLevel="2">
       <c r="A337" s="4" t="n">
-        <v>82.75</v>
+        <v>83.75</v>
       </c>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6" t="n"/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="338" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A338" s="4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6" t="n"/>
@@ -4387,7 +4387,7 @@
     </row>
     <row r="339" hidden="1" outlineLevel="2">
       <c r="A339" s="4" t="n">
-        <v>83.25</v>
+        <v>84.25</v>
       </c>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6" t="n"/>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="340" hidden="1" outlineLevel="2">
       <c r="A340" s="4" t="n">
-        <v>83.5</v>
+        <v>84.5</v>
       </c>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6" t="n"/>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="341" hidden="1" outlineLevel="2">
       <c r="A341" s="4" t="n">
-        <v>83.75</v>
+        <v>84.75</v>
       </c>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6" t="n"/>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="342" collapsed="1">
       <c r="A342" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B342" s="5" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="343" hidden="1" outlineLevel="2">
       <c r="A343" s="4" t="n">
-        <v>84.25</v>
+        <v>85.25</v>
       </c>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6" t="n"/>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="344" hidden="1" outlineLevel="2">
       <c r="A344" s="4" t="n">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6" t="n"/>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="345" hidden="1" outlineLevel="2">
       <c r="A345" s="4" t="n">
-        <v>84.75</v>
+        <v>85.75</v>
       </c>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6" t="n"/>
@@ -4480,7 +4480,7 @@
     </row>
     <row r="346" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A346" s="4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6" t="n"/>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="347" hidden="1" outlineLevel="2">
       <c r="A347" s="4" t="n">
-        <v>85.25</v>
+        <v>86.25</v>
       </c>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6" t="n"/>
@@ -4502,7 +4502,7 @@
     </row>
     <row r="348" hidden="1" outlineLevel="2">
       <c r="A348" s="4" t="n">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6" t="n"/>
@@ -4513,7 +4513,7 @@
     </row>
     <row r="349" hidden="1" outlineLevel="2">
       <c r="A349" s="4" t="n">
-        <v>85.75</v>
+        <v>86.75</v>
       </c>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6" t="n"/>
@@ -4524,7 +4524,7 @@
     </row>
     <row r="350" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A350" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6" t="n"/>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="351" hidden="1" outlineLevel="2">
       <c r="A351" s="4" t="n">
-        <v>86.25</v>
+        <v>87.25</v>
       </c>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6" t="n"/>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="352" hidden="1" outlineLevel="2">
       <c r="A352" s="4" t="n">
-        <v>86.5</v>
+        <v>87.5</v>
       </c>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6" t="n"/>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="353" hidden="1" outlineLevel="2">
       <c r="A353" s="4" t="n">
-        <v>86.75</v>
+        <v>87.75</v>
       </c>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6" t="n"/>
@@ -4568,7 +4568,7 @@
     </row>
     <row r="354" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A354" s="4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6" t="n"/>
@@ -4579,7 +4579,7 @@
     </row>
     <row r="355" hidden="1" outlineLevel="2">
       <c r="A355" s="4" t="n">
-        <v>87.25</v>
+        <v>88.25</v>
       </c>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6" t="n"/>
@@ -4590,7 +4590,7 @@
     </row>
     <row r="356" hidden="1" outlineLevel="2">
       <c r="A356" s="4" t="n">
-        <v>87.5</v>
+        <v>88.5</v>
       </c>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6" t="n"/>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="357" hidden="1" outlineLevel="2">
       <c r="A357" s="4" t="n">
-        <v>87.75</v>
+        <v>88.75</v>
       </c>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6" t="n"/>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="358" collapsed="1">
       <c r="A358" s="4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="359" hidden="1" outlineLevel="2">
       <c r="A359" s="4" t="n">
-        <v>88.25</v>
+        <v>89.25</v>
       </c>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6" t="n"/>
@@ -4652,7 +4652,7 @@
     </row>
     <row r="360" hidden="1" outlineLevel="2">
       <c r="A360" s="4" t="n">
-        <v>88.5</v>
+        <v>89.5</v>
       </c>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6" t="n"/>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="361" hidden="1" outlineLevel="2">
       <c r="A361" s="4" t="n">
-        <v>88.75</v>
+        <v>89.75</v>
       </c>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6" t="n"/>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="362" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A362" s="4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6" t="n"/>
@@ -4685,7 +4685,7 @@
     </row>
     <row r="363" hidden="1" outlineLevel="2">
       <c r="A363" s="4" t="n">
-        <v>89.25</v>
+        <v>90.25</v>
       </c>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6" t="n"/>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="364" hidden="1" outlineLevel="2">
       <c r="A364" s="4" t="n">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6" t="n"/>
@@ -4707,7 +4707,7 @@
     </row>
     <row r="365" hidden="1" outlineLevel="2">
       <c r="A365" s="4" t="n">
-        <v>89.75</v>
+        <v>90.75</v>
       </c>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6" t="n"/>
@@ -4718,7 +4718,7 @@
     </row>
     <row r="366" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A366" s="4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6" t="n"/>
@@ -4729,7 +4729,7 @@
     </row>
     <row r="367" hidden="1" outlineLevel="2">
       <c r="A367" s="4" t="n">
-        <v>90.25</v>
+        <v>91.25</v>
       </c>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6" t="n"/>
@@ -4740,7 +4740,7 @@
     </row>
     <row r="368" hidden="1" outlineLevel="2">
       <c r="A368" s="4" t="n">
-        <v>90.5</v>
+        <v>91.5</v>
       </c>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6" t="n"/>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="369" hidden="1" outlineLevel="2">
       <c r="A369" s="4" t="n">
-        <v>90.75</v>
+        <v>91.75</v>
       </c>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6" t="n"/>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="370" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A370" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6" t="n"/>
@@ -4773,7 +4773,7 @@
     </row>
     <row r="371" hidden="1" outlineLevel="2">
       <c r="A371" s="4" t="n">
-        <v>91.25</v>
+        <v>92.25</v>
       </c>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6" t="n"/>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="372" hidden="1" outlineLevel="2">
       <c r="A372" s="4" t="n">
-        <v>91.5</v>
+        <v>92.5</v>
       </c>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6" t="n"/>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="373" hidden="1" outlineLevel="2">
       <c r="A373" s="4" t="n">
-        <v>91.75</v>
+        <v>92.75</v>
       </c>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6" t="n"/>
@@ -4806,7 +4806,7 @@
     </row>
     <row r="374" collapsed="1">
       <c r="A374" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B374" s="5" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
     </row>
     <row r="375" hidden="1" outlineLevel="2">
       <c r="A375" s="4" t="n">
-        <v>92.25</v>
+        <v>93.25</v>
       </c>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6" t="n"/>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="376" hidden="1" outlineLevel="2">
       <c r="A376" s="4" t="n">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6" t="n"/>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="377" hidden="1" outlineLevel="2">
       <c r="A377" s="4" t="n">
-        <v>92.75</v>
+        <v>93.75</v>
       </c>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6" t="n"/>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="378" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A378" s="4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6" t="n"/>
@@ -4879,7 +4879,7 @@
     </row>
     <row r="379" hidden="1" outlineLevel="2">
       <c r="A379" s="4" t="n">
-        <v>93.25</v>
+        <v>94.25</v>
       </c>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6" t="n"/>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="380" hidden="1" outlineLevel="2">
       <c r="A380" s="4" t="n">
-        <v>93.5</v>
+        <v>94.5</v>
       </c>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6" t="n"/>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="381" hidden="1" outlineLevel="2">
       <c r="A381" s="4" t="n">
-        <v>93.75</v>
+        <v>94.75</v>
       </c>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6" t="n"/>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="382" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A382" s="4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6" t="n"/>
@@ -4923,7 +4923,7 @@
     </row>
     <row r="383" hidden="1" outlineLevel="2">
       <c r="A383" s="4" t="n">
-        <v>94.25</v>
+        <v>95.25</v>
       </c>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6" t="n"/>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="384" hidden="1" outlineLevel="2">
       <c r="A384" s="4" t="n">
-        <v>94.5</v>
+        <v>95.5</v>
       </c>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6" t="n"/>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="385" hidden="1" outlineLevel="2">
       <c r="A385" s="4" t="n">
-        <v>94.75</v>
+        <v>95.75</v>
       </c>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6" t="n"/>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="386" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A386" s="4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6" t="n"/>
@@ -4967,7 +4967,7 @@
     </row>
     <row r="387" hidden="1" outlineLevel="2">
       <c r="A387" s="4" t="n">
-        <v>95.25</v>
+        <v>96.25</v>
       </c>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6" t="n"/>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="388" hidden="1" outlineLevel="2">
       <c r="A388" s="4" t="n">
-        <v>95.5</v>
+        <v>96.5</v>
       </c>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6" t="n"/>
@@ -4989,7 +4989,7 @@
     </row>
     <row r="389" hidden="1" outlineLevel="2">
       <c r="A389" s="4" t="n">
-        <v>95.75</v>
+        <v>96.75</v>
       </c>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6" t="n"/>
@@ -5000,7 +5000,7 @@
     </row>
     <row r="390" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A390" s="4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6" t="n"/>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="391" hidden="1" outlineLevel="2">
       <c r="A391" s="4" t="n">
-        <v>96.25</v>
+        <v>97.25</v>
       </c>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6" t="n"/>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="392" hidden="1" outlineLevel="2">
       <c r="A392" s="4" t="n">
-        <v>96.5</v>
+        <v>97.5</v>
       </c>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6" t="n"/>
@@ -5033,7 +5033,7 @@
     </row>
     <row r="393" hidden="1" outlineLevel="2">
       <c r="A393" s="4" t="n">
-        <v>96.75</v>
+        <v>97.75</v>
       </c>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6" t="n"/>
@@ -5044,7 +5044,7 @@
     </row>
     <row r="394" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A394" s="4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6" t="n"/>
@@ -5055,7 +5055,7 @@
     </row>
     <row r="395" hidden="1" outlineLevel="2">
       <c r="A395" s="4" t="n">
-        <v>97.25</v>
+        <v>98.25</v>
       </c>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6" t="n"/>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="396" hidden="1" outlineLevel="2">
       <c r="A396" s="4" t="n">
-        <v>97.5</v>
+        <v>98.5</v>
       </c>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6" t="n"/>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="397" hidden="1" outlineLevel="2">
       <c r="A397" s="4" t="n">
-        <v>97.75</v>
+        <v>98.75</v>
       </c>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6" t="n"/>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="398" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A398" s="4" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6" t="n"/>
@@ -5099,7 +5099,7 @@
     </row>
     <row r="399" hidden="1" outlineLevel="2">
       <c r="A399" s="4" t="n">
-        <v>98.25</v>
+        <v>99.25</v>
       </c>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6" t="n"/>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="400" hidden="1" outlineLevel="2">
       <c r="A400" s="4" t="n">
-        <v>98.5</v>
+        <v>99.5</v>
       </c>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6" t="n"/>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="401" hidden="1" outlineLevel="2">
       <c r="A401" s="4" t="n">
-        <v>98.75</v>
+        <v>99.75</v>
       </c>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6" t="n"/>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="402" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A402" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6" t="n"/>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="403" hidden="1" outlineLevel="2">
       <c r="A403" s="4" t="n">
-        <v>99.25</v>
+        <v>100.25</v>
       </c>
       <c r="B403" s="5" t="n"/>
       <c r="C403" s="6" t="n"/>
@@ -5154,7 +5154,7 @@
     </row>
     <row r="404" hidden="1" outlineLevel="2">
       <c r="A404" s="4" t="n">
-        <v>99.5</v>
+        <v>100.5</v>
       </c>
       <c r="B404" s="5" t="n"/>
       <c r="C404" s="6" t="n"/>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="405" hidden="1" outlineLevel="2">
       <c r="A405" s="4" t="n">
-        <v>99.75</v>
+        <v>100.75</v>
       </c>
       <c r="B405" s="5" t="n"/>
       <c r="C405" s="6" t="n"/>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="406" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A406" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B406" s="5" t="n"/>
       <c r="C406" s="6" t="n"/>
@@ -5187,7 +5187,7 @@
     </row>
     <row r="407" hidden="1" outlineLevel="2">
       <c r="A407" s="4" t="n">
-        <v>100.25</v>
+        <v>101.25</v>
       </c>
       <c r="B407" s="5" t="n"/>
       <c r="C407" s="6" t="n"/>
@@ -5198,7 +5198,7 @@
     </row>
     <row r="408" hidden="1" outlineLevel="2">
       <c r="A408" s="4" t="n">
-        <v>100.5</v>
+        <v>101.5</v>
       </c>
       <c r="B408" s="5" t="n"/>
       <c r="C408" s="6" t="n"/>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="409" hidden="1" outlineLevel="2">
       <c r="A409" s="4" t="n">
-        <v>100.75</v>
+        <v>101.75</v>
       </c>
       <c r="B409" s="5" t="n"/>
       <c r="C409" s="6" t="n"/>
@@ -5220,7 +5220,7 @@
     </row>
     <row r="410" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A410" s="4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B410" s="5" t="n"/>
       <c r="C410" s="6" t="n"/>
@@ -5231,7 +5231,7 @@
     </row>
     <row r="411" hidden="1" outlineLevel="2">
       <c r="A411" s="4" t="n">
-        <v>101.25</v>
+        <v>102.25</v>
       </c>
       <c r="B411" s="5" t="n"/>
       <c r="C411" s="6" t="n"/>
@@ -5242,7 +5242,7 @@
     </row>
     <row r="412" hidden="1" outlineLevel="2">
       <c r="A412" s="4" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="B412" s="5" t="n"/>
       <c r="C412" s="6" t="n"/>
@@ -5253,7 +5253,7 @@
     </row>
     <row r="413" hidden="1" outlineLevel="2">
       <c r="A413" s="4" t="n">
-        <v>101.75</v>
+        <v>102.75</v>
       </c>
       <c r="B413" s="5" t="n"/>
       <c r="C413" s="6" t="n"/>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="414" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A414" s="4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B414" s="5" t="n"/>
       <c r="C414" s="6" t="n"/>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="415" hidden="1" outlineLevel="2">
       <c r="A415" s="4" t="n">
-        <v>102.25</v>
+        <v>103.25</v>
       </c>
       <c r="B415" s="5" t="n"/>
       <c r="C415" s="6" t="n"/>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="416" hidden="1" outlineLevel="2">
       <c r="A416" s="4" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="B416" s="5" t="n"/>
       <c r="C416" s="6" t="n"/>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="417" hidden="1" outlineLevel="2">
       <c r="A417" s="4" t="n">
-        <v>102.75</v>
+        <v>103.75</v>
       </c>
       <c r="B417" s="5" t="n"/>
       <c r="C417" s="6" t="n"/>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="418" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A418" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B418" s="5" t="n"/>
       <c r="C418" s="6" t="n"/>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="419" hidden="1" outlineLevel="2">
       <c r="A419" s="4" t="n">
-        <v>103.25</v>
+        <v>104.25</v>
       </c>
       <c r="B419" s="5" t="n"/>
       <c r="C419" s="6" t="n"/>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="420" hidden="1" outlineLevel="2">
       <c r="A420" s="4" t="n">
-        <v>103.5</v>
+        <v>104.5</v>
       </c>
       <c r="B420" s="5" t="n"/>
       <c r="C420" s="6" t="n"/>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="421" hidden="1" outlineLevel="2">
       <c r="A421" s="4" t="n">
-        <v>103.75</v>
+        <v>104.75</v>
       </c>
       <c r="B421" s="5" t="n"/>
       <c r="C421" s="6" t="n"/>
@@ -5352,7 +5352,7 @@
     </row>
     <row r="422" collapsed="1">
       <c r="A422" s="4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B422" s="5" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="423" hidden="1" outlineLevel="2">
       <c r="A423" s="4" t="n">
-        <v>104.25</v>
+        <v>105.25</v>
       </c>
       <c r="B423" s="5" t="n"/>
       <c r="C423" s="6" t="n"/>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="424" hidden="1" outlineLevel="2">
       <c r="A424" s="4" t="n">
-        <v>104.5</v>
+        <v>105.5</v>
       </c>
       <c r="B424" s="5" t="n"/>
       <c r="C424" s="6" t="n"/>
@@ -5403,7 +5403,7 @@
     </row>
     <row r="425" hidden="1" outlineLevel="2">
       <c r="A425" s="4" t="n">
-        <v>104.75</v>
+        <v>105.75</v>
       </c>
       <c r="B425" s="5" t="n"/>
       <c r="C425" s="6" t="n"/>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="426" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A426" s="4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B426" s="5" t="n"/>
       <c r="C426" s="6" t="n"/>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="427" hidden="1" outlineLevel="2">
       <c r="A427" s="4" t="n">
-        <v>105.25</v>
+        <v>106.25</v>
       </c>
       <c r="B427" s="5" t="n"/>
       <c r="C427" s="6" t="n"/>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="428" hidden="1" outlineLevel="2">
       <c r="A428" s="4" t="n">
-        <v>105.5</v>
+        <v>106.5</v>
       </c>
       <c r="B428" s="5" t="n"/>
       <c r="C428" s="6" t="n"/>
@@ -5447,7 +5447,7 @@
     </row>
     <row r="429" hidden="1" outlineLevel="2">
       <c r="A429" s="4" t="n">
-        <v>105.75</v>
+        <v>106.75</v>
       </c>
       <c r="B429" s="5" t="n"/>
       <c r="C429" s="6" t="n"/>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="430" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A430" s="4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B430" s="5" t="n"/>
       <c r="C430" s="6" t="n"/>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="431" hidden="1" outlineLevel="2">
       <c r="A431" s="4" t="n">
-        <v>106.25</v>
+        <v>107.25</v>
       </c>
       <c r="B431" s="5" t="n"/>
       <c r="C431" s="6" t="n"/>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="432" hidden="1" outlineLevel="2">
       <c r="A432" s="4" t="n">
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
       <c r="B432" s="5" t="n"/>
       <c r="C432" s="6" t="n"/>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="433" hidden="1" outlineLevel="2">
       <c r="A433" s="4" t="n">
-        <v>106.75</v>
+        <v>107.75</v>
       </c>
       <c r="B433" s="5" t="n"/>
       <c r="C433" s="6" t="n"/>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="434" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A434" s="4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B434" s="5" t="n"/>
       <c r="C434" s="6" t="n"/>
@@ -5513,7 +5513,7 @@
     </row>
     <row r="435" hidden="1" outlineLevel="2">
       <c r="A435" s="4" t="n">
-        <v>107.25</v>
+        <v>108.25</v>
       </c>
       <c r="B435" s="5" t="n"/>
       <c r="C435" s="6" t="n"/>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="436" hidden="1" outlineLevel="2">
       <c r="A436" s="4" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="B436" s="5" t="n"/>
       <c r="C436" s="6" t="n"/>
@@ -5535,7 +5535,7 @@
     </row>
     <row r="437" hidden="1" outlineLevel="2">
       <c r="A437" s="4" t="n">
-        <v>107.75</v>
+        <v>108.75</v>
       </c>
       <c r="B437" s="5" t="n"/>
       <c r="C437" s="6" t="n"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="438" collapsed="1">
       <c r="A438" s="4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B438" s="5" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
     </row>
     <row r="439" hidden="1" outlineLevel="2">
       <c r="A439" s="4" t="n">
-        <v>108.25</v>
+        <v>109.25</v>
       </c>
       <c r="B439" s="5" t="n"/>
       <c r="C439" s="6" t="n"/>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="440" hidden="1" outlineLevel="2">
       <c r="A440" s="4" t="n">
-        <v>108.5</v>
+        <v>109.5</v>
       </c>
       <c r="B440" s="5" t="n"/>
       <c r="C440" s="6" t="n"/>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="441" hidden="1" outlineLevel="2">
       <c r="A441" s="4" t="n">
-        <v>108.75</v>
+        <v>109.75</v>
       </c>
       <c r="B441" s="5" t="n"/>
       <c r="C441" s="6" t="n"/>
@@ -5606,7 +5606,7 @@
     </row>
     <row r="442" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A442" s="4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B442" s="5" t="n"/>
       <c r="C442" s="6" t="n"/>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="443" hidden="1" outlineLevel="2">
       <c r="A443" s="4" t="n">
-        <v>109.25</v>
+        <v>110.25</v>
       </c>
       <c r="B443" s="5" t="n"/>
       <c r="C443" s="6" t="n"/>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="444" hidden="1" outlineLevel="2">
       <c r="A444" s="4" t="n">
-        <v>109.5</v>
+        <v>110.5</v>
       </c>
       <c r="B444" s="5" t="n"/>
       <c r="C444" s="6" t="n"/>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="445" hidden="1" outlineLevel="2">
       <c r="A445" s="4" t="n">
-        <v>109.75</v>
+        <v>110.75</v>
       </c>
       <c r="B445" s="5" t="n"/>
       <c r="C445" s="6" t="n"/>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="446" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A446" s="4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B446" s="5" t="n"/>
       <c r="C446" s="6" t="n"/>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="447" hidden="1" outlineLevel="2">
       <c r="A447" s="4" t="n">
-        <v>110.25</v>
+        <v>111.25</v>
       </c>
       <c r="B447" s="5" t="n"/>
       <c r="C447" s="6" t="n"/>
@@ -5672,7 +5672,7 @@
     </row>
     <row r="448" hidden="1" outlineLevel="2">
       <c r="A448" s="4" t="n">
-        <v>110.5</v>
+        <v>111.5</v>
       </c>
       <c r="B448" s="5" t="n"/>
       <c r="C448" s="6" t="n"/>
@@ -5683,7 +5683,7 @@
     </row>
     <row r="449" hidden="1" outlineLevel="2">
       <c r="A449" s="4" t="n">
-        <v>110.75</v>
+        <v>111.75</v>
       </c>
       <c r="B449" s="5" t="n"/>
       <c r="C449" s="6" t="n"/>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="450" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A450" s="4" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B450" s="5" t="n"/>
       <c r="C450" s="6" t="n"/>
@@ -5705,7 +5705,7 @@
     </row>
     <row r="451" hidden="1" outlineLevel="2">
       <c r="A451" s="4" t="n">
-        <v>111.25</v>
+        <v>112.25</v>
       </c>
       <c r="B451" s="5" t="n"/>
       <c r="C451" s="6" t="n"/>
@@ -5716,7 +5716,7 @@
     </row>
     <row r="452" hidden="1" outlineLevel="2">
       <c r="A452" s="4" t="n">
-        <v>111.5</v>
+        <v>112.5</v>
       </c>
       <c r="B452" s="5" t="n"/>
       <c r="C452" s="6" t="n"/>
@@ -5727,7 +5727,7 @@
     </row>
     <row r="453" hidden="1" outlineLevel="2">
       <c r="A453" s="4" t="n">
-        <v>111.75</v>
+        <v>112.75</v>
       </c>
       <c r="B453" s="5" t="n"/>
       <c r="C453" s="6" t="n"/>
@@ -5738,7 +5738,7 @@
     </row>
     <row r="454" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A454" s="4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B454" s="5" t="n"/>
       <c r="C454" s="6" t="n"/>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="455" hidden="1" outlineLevel="2">
       <c r="A455" s="4" t="n">
-        <v>112.25</v>
+        <v>113.25</v>
       </c>
       <c r="B455" s="5" t="n"/>
       <c r="C455" s="6" t="n"/>
@@ -5760,7 +5760,7 @@
     </row>
     <row r="456" hidden="1" outlineLevel="2">
       <c r="A456" s="4" t="n">
-        <v>112.5</v>
+        <v>113.5</v>
       </c>
       <c r="B456" s="5" t="n"/>
       <c r="C456" s="6" t="n"/>
@@ -5771,7 +5771,7 @@
     </row>
     <row r="457" hidden="1" outlineLevel="2">
       <c r="A457" s="4" t="n">
-        <v>112.75</v>
+        <v>113.75</v>
       </c>
       <c r="B457" s="5" t="n"/>
       <c r="C457" s="6" t="n"/>
@@ -5782,7 +5782,7 @@
     </row>
     <row r="458" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A458" s="4" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B458" s="5" t="n"/>
       <c r="C458" s="6" t="n"/>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="459" hidden="1" outlineLevel="2">
       <c r="A459" s="4" t="n">
-        <v>113.25</v>
+        <v>114.25</v>
       </c>
       <c r="B459" s="5" t="n"/>
       <c r="C459" s="6" t="n"/>
@@ -5804,7 +5804,7 @@
     </row>
     <row r="460" hidden="1" outlineLevel="2">
       <c r="A460" s="4" t="n">
-        <v>113.5</v>
+        <v>114.5</v>
       </c>
       <c r="B460" s="5" t="n"/>
       <c r="C460" s="6" t="n"/>
@@ -5815,7 +5815,7 @@
     </row>
     <row r="461" hidden="1" outlineLevel="2">
       <c r="A461" s="4" t="n">
-        <v>113.75</v>
+        <v>114.75</v>
       </c>
       <c r="B461" s="5" t="n"/>
       <c r="C461" s="6" t="n"/>
@@ -5826,7 +5826,7 @@
     </row>
     <row r="462" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A462" s="4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B462" s="5" t="n"/>
       <c r="C462" s="6" t="n"/>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="463" hidden="1" outlineLevel="2">
       <c r="A463" s="4" t="n">
-        <v>114.25</v>
+        <v>115.25</v>
       </c>
       <c r="B463" s="5" t="n"/>
       <c r="C463" s="6" t="n"/>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="464" hidden="1" outlineLevel="2">
       <c r="A464" s="4" t="n">
-        <v>114.5</v>
+        <v>115.5</v>
       </c>
       <c r="B464" s="5" t="n"/>
       <c r="C464" s="6" t="n"/>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="465" hidden="1" outlineLevel="2">
       <c r="A465" s="4" t="n">
-        <v>114.75</v>
+        <v>115.75</v>
       </c>
       <c r="B465" s="5" t="n"/>
       <c r="C465" s="6" t="n"/>
@@ -5870,7 +5870,7 @@
     </row>
     <row r="466" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A466" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B466" s="5" t="n"/>
       <c r="C466" s="6" t="n"/>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="467" hidden="1" outlineLevel="2">
       <c r="A467" s="4" t="n">
-        <v>115.25</v>
+        <v>116.25</v>
       </c>
       <c r="B467" s="5" t="n"/>
       <c r="C467" s="6" t="n"/>
@@ -5892,7 +5892,7 @@
     </row>
     <row r="468" hidden="1" outlineLevel="2">
       <c r="A468" s="4" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="B468" s="5" t="n"/>
       <c r="C468" s="6" t="n"/>
@@ -5903,7 +5903,7 @@
     </row>
     <row r="469" hidden="1" outlineLevel="2">
       <c r="A469" s="4" t="n">
-        <v>115.75</v>
+        <v>116.75</v>
       </c>
       <c r="B469" s="5" t="n"/>
       <c r="C469" s="6" t="n"/>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="470" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A470" s="4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B470" s="5" t="n"/>
       <c r="C470" s="6" t="n"/>
@@ -5925,7 +5925,7 @@
     </row>
     <row r="471" hidden="1" outlineLevel="2">
       <c r="A471" s="4" t="n">
-        <v>116.25</v>
+        <v>117.25</v>
       </c>
       <c r="B471" s="5" t="n"/>
       <c r="C471" s="6" t="n"/>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="472" hidden="1" outlineLevel="2">
       <c r="A472" s="4" t="n">
-        <v>116.5</v>
+        <v>117.5</v>
       </c>
       <c r="B472" s="5" t="n"/>
       <c r="C472" s="6" t="n"/>
@@ -5947,7 +5947,7 @@
     </row>
     <row r="473" hidden="1" outlineLevel="2">
       <c r="A473" s="4" t="n">
-        <v>116.75</v>
+        <v>117.75</v>
       </c>
       <c r="B473" s="5" t="n"/>
       <c r="C473" s="6" t="n"/>
@@ -5958,7 +5958,7 @@
     </row>
     <row r="474" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A474" s="4" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B474" s="5" t="n"/>
       <c r="C474" s="6" t="n"/>
@@ -5969,7 +5969,7 @@
     </row>
     <row r="475" hidden="1" outlineLevel="2">
       <c r="A475" s="4" t="n">
-        <v>117.25</v>
+        <v>118.25</v>
       </c>
       <c r="B475" s="5" t="n"/>
       <c r="C475" s="6" t="n"/>
@@ -5980,7 +5980,7 @@
     </row>
     <row r="476" hidden="1" outlineLevel="2">
       <c r="A476" s="4" t="n">
-        <v>117.5</v>
+        <v>118.5</v>
       </c>
       <c r="B476" s="5" t="n"/>
       <c r="C476" s="6" t="n"/>
@@ -5991,7 +5991,7 @@
     </row>
     <row r="477" hidden="1" outlineLevel="2">
       <c r="A477" s="4" t="n">
-        <v>117.75</v>
+        <v>118.75</v>
       </c>
       <c r="B477" s="5" t="n"/>
       <c r="C477" s="6" t="n"/>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="478" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A478" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B478" s="5" t="n"/>
       <c r="C478" s="6" t="n"/>
@@ -6013,7 +6013,7 @@
     </row>
     <row r="479" hidden="1" outlineLevel="2">
       <c r="A479" s="4" t="n">
-        <v>118.25</v>
+        <v>119.25</v>
       </c>
       <c r="B479" s="5" t="n"/>
       <c r="C479" s="6" t="n"/>
@@ -6024,7 +6024,7 @@
     </row>
     <row r="480" hidden="1" outlineLevel="2">
       <c r="A480" s="4" t="n">
-        <v>118.5</v>
+        <v>119.5</v>
       </c>
       <c r="B480" s="5" t="n"/>
       <c r="C480" s="6" t="n"/>
@@ -6035,7 +6035,7 @@
     </row>
     <row r="481" hidden="1" outlineLevel="2">
       <c r="A481" s="4" t="n">
-        <v>118.75</v>
+        <v>119.75</v>
       </c>
       <c r="B481" s="5" t="n"/>
       <c r="C481" s="6" t="n"/>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="482" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A482" s="4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B482" s="5" t="n"/>
       <c r="C482" s="6" t="n"/>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="483" hidden="1" outlineLevel="2">
       <c r="A483" s="4" t="n">
-        <v>119.25</v>
+        <v>120.25</v>
       </c>
       <c r="B483" s="5" t="n"/>
       <c r="C483" s="6" t="n"/>
@@ -6068,7 +6068,7 @@
     </row>
     <row r="484" hidden="1" outlineLevel="2">
       <c r="A484" s="4" t="n">
-        <v>119.5</v>
+        <v>120.5</v>
       </c>
       <c r="B484" s="5" t="n"/>
       <c r="C484" s="6" t="n"/>
@@ -6079,7 +6079,7 @@
     </row>
     <row r="485" hidden="1" outlineLevel="2">
       <c r="A485" s="4" t="n">
-        <v>119.75</v>
+        <v>120.75</v>
       </c>
       <c r="B485" s="5" t="n"/>
       <c r="C485" s="6" t="n"/>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="486" collapsed="1">
       <c r="A486" s="4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B486" s="5" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
     </row>
     <row r="487" hidden="1" outlineLevel="2">
       <c r="A487" s="4" t="n">
-        <v>120.25</v>
+        <v>121.25</v>
       </c>
       <c r="B487" s="5" t="n"/>
       <c r="C487" s="6" t="n"/>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="488" hidden="1" outlineLevel="2">
       <c r="A488" s="4" t="n">
-        <v>120.5</v>
+        <v>121.5</v>
       </c>
       <c r="B488" s="5" t="n"/>
       <c r="C488" s="6" t="n"/>
@@ -6139,7 +6139,7 @@
     </row>
     <row r="489" hidden="1" outlineLevel="2">
       <c r="A489" s="4" t="n">
-        <v>120.75</v>
+        <v>121.75</v>
       </c>
       <c r="B489" s="5" t="n"/>
       <c r="C489" s="6" t="n"/>
@@ -6150,7 +6150,7 @@
     </row>
     <row r="490" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A490" s="4" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B490" s="5" t="n"/>
       <c r="C490" s="6" t="n"/>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="491" hidden="1" outlineLevel="2">
       <c r="A491" s="4" t="n">
-        <v>121.25</v>
+        <v>122.25</v>
       </c>
       <c r="B491" s="5" t="n"/>
       <c r="C491" s="6" t="n"/>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="492" hidden="1" outlineLevel="2">
       <c r="A492" s="4" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="B492" s="5" t="n"/>
       <c r="C492" s="6" t="n"/>
@@ -6183,7 +6183,7 @@
     </row>
     <row r="493" hidden="1" outlineLevel="2">
       <c r="A493" s="4" t="n">
-        <v>121.75</v>
+        <v>122.75</v>
       </c>
       <c r="B493" s="5" t="n"/>
       <c r="C493" s="6" t="n"/>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="494" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A494" s="4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B494" s="5" t="n"/>
       <c r="C494" s="6" t="n"/>
@@ -6205,7 +6205,7 @@
     </row>
     <row r="495" hidden="1" outlineLevel="2">
       <c r="A495" s="4" t="n">
-        <v>122.25</v>
+        <v>123.25</v>
       </c>
       <c r="B495" s="5" t="n"/>
       <c r="C495" s="6" t="n"/>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="496" hidden="1" outlineLevel="2">
       <c r="A496" s="4" t="n">
-        <v>122.5</v>
+        <v>123.5</v>
       </c>
       <c r="B496" s="5" t="n"/>
       <c r="C496" s="6" t="n"/>
@@ -6227,7 +6227,7 @@
     </row>
     <row r="497" hidden="1" outlineLevel="2">
       <c r="A497" s="4" t="n">
-        <v>122.75</v>
+        <v>123.75</v>
       </c>
       <c r="B497" s="5" t="n"/>
       <c r="C497" s="6" t="n"/>
@@ -6238,7 +6238,7 @@
     </row>
     <row r="498" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A498" s="4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B498" s="5" t="n"/>
       <c r="C498" s="6" t="n"/>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="499" hidden="1" outlineLevel="2">
       <c r="A499" s="4" t="n">
-        <v>123.25</v>
+        <v>124.25</v>
       </c>
       <c r="B499" s="5" t="n"/>
       <c r="C499" s="6" t="n"/>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="500" hidden="1" outlineLevel="2">
       <c r="A500" s="4" t="n">
-        <v>123.5</v>
+        <v>124.5</v>
       </c>
       <c r="B500" s="5" t="n"/>
       <c r="C500" s="6" t="n"/>
@@ -6271,7 +6271,7 @@
     </row>
     <row r="501" hidden="1" outlineLevel="2">
       <c r="A501" s="4" t="n">
-        <v>123.75</v>
+        <v>124.75</v>
       </c>
       <c r="B501" s="5" t="n"/>
       <c r="C501" s="6" t="n"/>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="502" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A502" s="4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B502" s="5" t="n"/>
       <c r="C502" s="6" t="n"/>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="503" hidden="1" outlineLevel="2">
       <c r="A503" s="4" t="n">
-        <v>124.25</v>
+        <v>125.25</v>
       </c>
       <c r="B503" s="5" t="n"/>
       <c r="C503" s="6" t="n"/>
@@ -6304,7 +6304,7 @@
     </row>
     <row r="504" hidden="1" outlineLevel="2">
       <c r="A504" s="4" t="n">
-        <v>124.5</v>
+        <v>125.5</v>
       </c>
       <c r="B504" s="5" t="n"/>
       <c r="C504" s="6" t="n"/>
@@ -6315,7 +6315,7 @@
     </row>
     <row r="505" hidden="1" outlineLevel="2">
       <c r="A505" s="4" t="n">
-        <v>124.75</v>
+        <v>125.75</v>
       </c>
       <c r="B505" s="5" t="n"/>
       <c r="C505" s="6" t="n"/>
@@ -6326,7 +6326,7 @@
     </row>
     <row r="506" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A506" s="4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B506" s="5" t="n"/>
       <c r="C506" s="6" t="n"/>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="507" hidden="1" outlineLevel="2">
       <c r="A507" s="4" t="n">
-        <v>125.25</v>
+        <v>126.25</v>
       </c>
       <c r="B507" s="5" t="n"/>
       <c r="C507" s="6" t="n"/>
@@ -6348,7 +6348,7 @@
     </row>
     <row r="508" hidden="1" outlineLevel="2">
       <c r="A508" s="4" t="n">
-        <v>125.5</v>
+        <v>126.5</v>
       </c>
       <c r="B508" s="5" t="n"/>
       <c r="C508" s="6" t="n"/>
@@ -6359,7 +6359,7 @@
     </row>
     <row r="509" hidden="1" outlineLevel="2">
       <c r="A509" s="4" t="n">
-        <v>125.75</v>
+        <v>126.75</v>
       </c>
       <c r="B509" s="5" t="n"/>
       <c r="C509" s="6" t="n"/>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="510" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A510" s="4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B510" s="5" t="n"/>
       <c r="C510" s="6" t="n"/>
@@ -6381,7 +6381,7 @@
     </row>
     <row r="511" hidden="1" outlineLevel="2">
       <c r="A511" s="4" t="n">
-        <v>126.25</v>
+        <v>127.25</v>
       </c>
       <c r="B511" s="5" t="n"/>
       <c r="C511" s="6" t="n"/>
@@ -6392,7 +6392,7 @@
     </row>
     <row r="512" hidden="1" outlineLevel="2">
       <c r="A512" s="4" t="n">
-        <v>126.5</v>
+        <v>127.5</v>
       </c>
       <c r="B512" s="5" t="n"/>
       <c r="C512" s="6" t="n"/>
@@ -6403,7 +6403,7 @@
     </row>
     <row r="513" hidden="1" outlineLevel="2">
       <c r="A513" s="4" t="n">
-        <v>126.75</v>
+        <v>127.75</v>
       </c>
       <c r="B513" s="5" t="n"/>
       <c r="C513" s="6" t="n"/>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="514" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A514" s="4" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B514" s="5" t="n"/>
       <c r="C514" s="6" t="n"/>
@@ -6425,7 +6425,7 @@
     </row>
     <row r="515" hidden="1" outlineLevel="2">
       <c r="A515" s="4" t="n">
-        <v>127.25</v>
+        <v>128.25</v>
       </c>
       <c r="B515" s="5" t="n"/>
       <c r="C515" s="6" t="n"/>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="516" hidden="1" outlineLevel="2">
       <c r="A516" s="4" t="n">
-        <v>127.5</v>
+        <v>128.5</v>
       </c>
       <c r="B516" s="5" t="n"/>
       <c r="C516" s="6" t="n"/>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="517" hidden="1" outlineLevel="2">
       <c r="A517" s="4" t="n">
-        <v>127.75</v>
+        <v>128.75</v>
       </c>
       <c r="B517" s="5" t="n"/>
       <c r="C517" s="6" t="n"/>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="518" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A518" s="4" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B518" s="5" t="n"/>
       <c r="C518" s="6" t="n"/>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="519" hidden="1" outlineLevel="2">
       <c r="A519" s="4" t="n">
-        <v>128.25</v>
+        <v>129.25</v>
       </c>
       <c r="B519" s="5" t="n"/>
       <c r="C519" s="6" t="n"/>
@@ -6480,7 +6480,7 @@
     </row>
     <row r="520" hidden="1" outlineLevel="2">
       <c r="A520" s="4" t="n">
-        <v>128.5</v>
+        <v>129.5</v>
       </c>
       <c r="B520" s="5" t="n"/>
       <c r="C520" s="6" t="n"/>
@@ -6491,7 +6491,7 @@
     </row>
     <row r="521" hidden="1" outlineLevel="2">
       <c r="A521" s="4" t="n">
-        <v>128.75</v>
+        <v>129.75</v>
       </c>
       <c r="B521" s="5" t="n"/>
       <c r="C521" s="6" t="n"/>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="522" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A522" s="4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B522" s="5" t="n"/>
       <c r="C522" s="6" t="n"/>
@@ -6513,7 +6513,7 @@
     </row>
     <row r="523" hidden="1" outlineLevel="2">
       <c r="A523" s="4" t="n">
-        <v>129.25</v>
+        <v>130.25</v>
       </c>
       <c r="B523" s="5" t="n"/>
       <c r="C523" s="6" t="n"/>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="524" hidden="1" outlineLevel="2">
       <c r="A524" s="4" t="n">
-        <v>129.5</v>
+        <v>130.5</v>
       </c>
       <c r="B524" s="5" t="n"/>
       <c r="C524" s="6" t="n"/>
@@ -6535,7 +6535,7 @@
     </row>
     <row r="525" hidden="1" outlineLevel="2">
       <c r="A525" s="4" t="n">
-        <v>129.75</v>
+        <v>130.75</v>
       </c>
       <c r="B525" s="5" t="n"/>
       <c r="C525" s="6" t="n"/>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="526" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A526" s="4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B526" s="5" t="n"/>
       <c r="C526" s="6" t="n"/>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="527" hidden="1" outlineLevel="2">
       <c r="A527" s="4" t="n">
-        <v>130.25</v>
+        <v>131.25</v>
       </c>
       <c r="B527" s="5" t="n"/>
       <c r="C527" s="6" t="n"/>
@@ -6568,7 +6568,7 @@
     </row>
     <row r="528" hidden="1" outlineLevel="2">
       <c r="A528" s="4" t="n">
-        <v>130.5</v>
+        <v>131.5</v>
       </c>
       <c r="B528" s="5" t="n"/>
       <c r="C528" s="6" t="n"/>
@@ -6579,7 +6579,7 @@
     </row>
     <row r="529" hidden="1" outlineLevel="2">
       <c r="A529" s="4" t="n">
-        <v>130.75</v>
+        <v>131.75</v>
       </c>
       <c r="B529" s="5" t="n"/>
       <c r="C529" s="6" t="n"/>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="530" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A530" s="4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B530" s="5" t="n"/>
       <c r="C530" s="6" t="n"/>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="531" hidden="1" outlineLevel="2">
       <c r="A531" s="4" t="n">
-        <v>131.25</v>
+        <v>132.25</v>
       </c>
       <c r="B531" s="5" t="n"/>
       <c r="C531" s="6" t="n"/>
@@ -6612,7 +6612,7 @@
     </row>
     <row r="532" hidden="1" outlineLevel="2">
       <c r="A532" s="4" t="n">
-        <v>131.5</v>
+        <v>132.5</v>
       </c>
       <c r="B532" s="5" t="n"/>
       <c r="C532" s="6" t="n"/>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="533" hidden="1" outlineLevel="2">
       <c r="A533" s="4" t="n">
-        <v>131.75</v>
+        <v>132.75</v>
       </c>
       <c r="B533" s="5" t="n"/>
       <c r="C533" s="6" t="n"/>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="534" collapsed="1">
       <c r="A534" s="4" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B534" s="5" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
     </row>
     <row r="535" hidden="1" outlineLevel="2">
       <c r="A535" s="4" t="n">
-        <v>132.25</v>
+        <v>133.25</v>
       </c>
       <c r="B535" s="5" t="n"/>
       <c r="C535" s="6" t="n"/>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="536" hidden="1" outlineLevel="2">
       <c r="A536" s="4" t="n">
-        <v>132.5</v>
+        <v>133.5</v>
       </c>
       <c r="B536" s="5" t="n"/>
       <c r="C536" s="6" t="n"/>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="537" hidden="1" outlineLevel="2">
       <c r="A537" s="4" t="n">
-        <v>132.75</v>
+        <v>133.75</v>
       </c>
       <c r="B537" s="5" t="n"/>
       <c r="C537" s="6" t="n"/>
@@ -6694,7 +6694,7 @@
     </row>
     <row r="538" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A538" s="4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B538" s="5" t="n"/>
       <c r="C538" s="6" t="n"/>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="539" hidden="1" outlineLevel="2">
       <c r="A539" s="4" t="n">
-        <v>133.25</v>
+        <v>134.25</v>
       </c>
       <c r="B539" s="5" t="n"/>
       <c r="C539" s="6" t="n"/>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="540" hidden="1" outlineLevel="2">
       <c r="A540" s="4" t="n">
-        <v>133.5</v>
+        <v>134.5</v>
       </c>
       <c r="B540" s="5" t="n"/>
       <c r="C540" s="6" t="n"/>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="541" hidden="1" outlineLevel="2">
       <c r="A541" s="4" t="n">
-        <v>133.75</v>
+        <v>134.75</v>
       </c>
       <c r="B541" s="5" t="n"/>
       <c r="C541" s="6" t="n"/>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="542" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A542" s="4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B542" s="5" t="n"/>
       <c r="C542" s="6" t="n"/>
@@ -6749,7 +6749,7 @@
     </row>
     <row r="543" hidden="1" outlineLevel="2">
       <c r="A543" s="4" t="n">
-        <v>134.25</v>
+        <v>135.25</v>
       </c>
       <c r="B543" s="5" t="n"/>
       <c r="C543" s="6" t="n"/>
@@ -6760,7 +6760,7 @@
     </row>
     <row r="544" hidden="1" outlineLevel="2">
       <c r="A544" s="4" t="n">
-        <v>134.5</v>
+        <v>135.5</v>
       </c>
       <c r="B544" s="5" t="n"/>
       <c r="C544" s="6" t="n"/>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="545" hidden="1" outlineLevel="2">
       <c r="A545" s="4" t="n">
-        <v>134.75</v>
+        <v>135.75</v>
       </c>
       <c r="B545" s="5" t="n"/>
       <c r="C545" s="6" t="n"/>
@@ -6782,7 +6782,7 @@
     </row>
     <row r="546" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A546" s="4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B546" s="5" t="n"/>
       <c r="C546" s="6" t="n"/>
@@ -6793,7 +6793,7 @@
     </row>
     <row r="547" hidden="1" outlineLevel="2">
       <c r="A547" s="4" t="n">
-        <v>135.25</v>
+        <v>136.25</v>
       </c>
       <c r="B547" s="5" t="n"/>
       <c r="C547" s="6" t="n"/>
@@ -6804,7 +6804,7 @@
     </row>
     <row r="548" hidden="1" outlineLevel="2">
       <c r="A548" s="4" t="n">
-        <v>135.5</v>
+        <v>136.5</v>
       </c>
       <c r="B548" s="5" t="n"/>
       <c r="C548" s="6" t="n"/>
@@ -6815,7 +6815,7 @@
     </row>
     <row r="549" hidden="1" outlineLevel="2">
       <c r="A549" s="4" t="n">
-        <v>135.75</v>
+        <v>136.75</v>
       </c>
       <c r="B549" s="5" t="n"/>
       <c r="C549" s="6" t="n"/>
@@ -6826,7 +6826,7 @@
     </row>
     <row r="550" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A550" s="4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B550" s="5" t="n"/>
       <c r="C550" s="6" t="n"/>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="551" hidden="1" outlineLevel="2">
       <c r="A551" s="4" t="n">
-        <v>136.25</v>
+        <v>137.25</v>
       </c>
       <c r="B551" s="5" t="n"/>
       <c r="C551" s="6" t="n"/>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="552" hidden="1" outlineLevel="2">
       <c r="A552" s="4" t="n">
-        <v>136.5</v>
+        <v>137.5</v>
       </c>
       <c r="B552" s="5" t="n"/>
       <c r="C552" s="6" t="n"/>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="553" hidden="1" outlineLevel="2">
       <c r="A553" s="4" t="n">
-        <v>136.75</v>
+        <v>137.75</v>
       </c>
       <c r="B553" s="5" t="n"/>
       <c r="C553" s="6" t="n"/>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="554" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A554" s="4" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B554" s="5" t="n"/>
       <c r="C554" s="6" t="n"/>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="555" hidden="1" outlineLevel="2">
       <c r="A555" s="4" t="n">
-        <v>137.25</v>
+        <v>138.25</v>
       </c>
       <c r="B555" s="5" t="n"/>
       <c r="C555" s="6" t="n"/>
@@ -6892,7 +6892,7 @@
     </row>
     <row r="556" hidden="1" outlineLevel="2">
       <c r="A556" s="4" t="n">
-        <v>137.5</v>
+        <v>138.5</v>
       </c>
       <c r="B556" s="5" t="n"/>
       <c r="C556" s="6" t="n"/>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="557" hidden="1" outlineLevel="2">
       <c r="A557" s="4" t="n">
-        <v>137.75</v>
+        <v>138.75</v>
       </c>
       <c r="B557" s="5" t="n"/>
       <c r="C557" s="6" t="n"/>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="558" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A558" s="4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B558" s="5" t="n"/>
       <c r="C558" s="6" t="n"/>
@@ -6925,7 +6925,7 @@
     </row>
     <row r="559" hidden="1" outlineLevel="2">
       <c r="A559" s="4" t="n">
-        <v>138.25</v>
+        <v>139.25</v>
       </c>
       <c r="B559" s="5" t="n"/>
       <c r="C559" s="6" t="n"/>
@@ -6936,7 +6936,7 @@
     </row>
     <row r="560" hidden="1" outlineLevel="2">
       <c r="A560" s="4" t="n">
-        <v>138.5</v>
+        <v>139.5</v>
       </c>
       <c r="B560" s="5" t="n"/>
       <c r="C560" s="6" t="n"/>
@@ -6947,7 +6947,7 @@
     </row>
     <row r="561" hidden="1" outlineLevel="2">
       <c r="A561" s="4" t="n">
-        <v>138.75</v>
+        <v>139.75</v>
       </c>
       <c r="B561" s="5" t="n"/>
       <c r="C561" s="6" t="n"/>
@@ -6958,7 +6958,7 @@
     </row>
     <row r="562" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A562" s="4" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B562" s="5" t="n"/>
       <c r="C562" s="6" t="n"/>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="563" hidden="1" outlineLevel="2">
       <c r="A563" s="4" t="n">
-        <v>139.25</v>
+        <v>140.25</v>
       </c>
       <c r="B563" s="5" t="n"/>
       <c r="C563" s="6" t="n"/>
@@ -6980,7 +6980,7 @@
     </row>
     <row r="564" hidden="1" outlineLevel="2">
       <c r="A564" s="4" t="n">
-        <v>139.5</v>
+        <v>140.5</v>
       </c>
       <c r="B564" s="5" t="n"/>
       <c r="C564" s="6" t="n"/>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="565" hidden="1" outlineLevel="2">
       <c r="A565" s="4" t="n">
-        <v>139.75</v>
+        <v>140.75</v>
       </c>
       <c r="B565" s="5" t="n"/>
       <c r="C565" s="6" t="n"/>
@@ -7002,7 +7002,7 @@
     </row>
     <row r="566" collapsed="1">
       <c r="A566" s="4" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B566" s="5" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
     </row>
     <row r="567" hidden="1" outlineLevel="2">
       <c r="A567" s="4" t="n">
-        <v>140.25</v>
+        <v>141.25</v>
       </c>
       <c r="B567" s="5" t="n"/>
       <c r="C567" s="6" t="n"/>
@@ -7040,7 +7040,7 @@
     </row>
     <row r="568" hidden="1" outlineLevel="2">
       <c r="A568" s="4" t="n">
-        <v>140.5</v>
+        <v>141.5</v>
       </c>
       <c r="B568" s="5" t="n"/>
       <c r="C568" s="6" t="n"/>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="569" hidden="1" outlineLevel="2">
       <c r="A569" s="4" t="n">
-        <v>140.75</v>
+        <v>141.75</v>
       </c>
       <c r="B569" s="5" t="n"/>
       <c r="C569" s="6" t="n"/>
@@ -7062,7 +7062,7 @@
     </row>
     <row r="570" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A570" s="4" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B570" s="5" t="n"/>
       <c r="C570" s="6" t="n"/>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="571" hidden="1" outlineLevel="2">
       <c r="A571" s="4" t="n">
-        <v>141.25</v>
+        <v>142.25</v>
       </c>
       <c r="B571" s="5" t="n"/>
       <c r="C571" s="6" t="n"/>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="572" hidden="1" outlineLevel="2">
       <c r="A572" s="4" t="n">
-        <v>141.5</v>
+        <v>142.5</v>
       </c>
       <c r="B572" s="5" t="n"/>
       <c r="C572" s="6" t="n"/>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="573" hidden="1" outlineLevel="2">
       <c r="A573" s="4" t="n">
-        <v>141.75</v>
+        <v>142.75</v>
       </c>
       <c r="B573" s="5" t="n"/>
       <c r="C573" s="6" t="n"/>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="574" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A574" s="4" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B574" s="5" t="n"/>
       <c r="C574" s="6" t="n"/>
@@ -7117,7 +7117,7 @@
     </row>
     <row r="575" hidden="1" outlineLevel="2">
       <c r="A575" s="4" t="n">
-        <v>142.25</v>
+        <v>143.25</v>
       </c>
       <c r="B575" s="5" t="n"/>
       <c r="C575" s="6" t="n"/>
@@ -7128,7 +7128,7 @@
     </row>
     <row r="576" hidden="1" outlineLevel="2">
       <c r="A576" s="4" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
       <c r="B576" s="5" t="n"/>
       <c r="C576" s="6" t="n"/>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="577" hidden="1" outlineLevel="2">
       <c r="A577" s="4" t="n">
-        <v>142.75</v>
+        <v>143.75</v>
       </c>
       <c r="B577" s="5" t="n"/>
       <c r="C577" s="6" t="n"/>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="578" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A578" s="4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B578" s="5" t="n"/>
       <c r="C578" s="6" t="n"/>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="579" hidden="1" outlineLevel="2">
       <c r="A579" s="4" t="n">
-        <v>143.25</v>
+        <v>144.25</v>
       </c>
       <c r="B579" s="5" t="n"/>
       <c r="C579" s="6" t="n"/>
@@ -7172,7 +7172,7 @@
     </row>
     <row r="580" hidden="1" outlineLevel="2">
       <c r="A580" s="4" t="n">
-        <v>143.5</v>
+        <v>144.5</v>
       </c>
       <c r="B580" s="5" t="n"/>
       <c r="C580" s="6" t="n"/>
@@ -7183,7 +7183,7 @@
     </row>
     <row r="581" hidden="1" outlineLevel="2">
       <c r="A581" s="4" t="n">
-        <v>143.75</v>
+        <v>144.75</v>
       </c>
       <c r="B581" s="5" t="n"/>
       <c r="C581" s="6" t="n"/>
@@ -7194,7 +7194,7 @@
     </row>
     <row r="582" collapsed="1">
       <c r="A582" s="4" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B582" s="5" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
     </row>
     <row r="583" hidden="1" outlineLevel="2">
       <c r="A583" s="4" t="n">
-        <v>144.25</v>
+        <v>145.25</v>
       </c>
       <c r="B583" s="5" t="n"/>
       <c r="C583" s="6" t="n"/>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="584" hidden="1" outlineLevel="2">
       <c r="A584" s="4" t="n">
-        <v>144.5</v>
+        <v>145.5</v>
       </c>
       <c r="B584" s="5" t="n"/>
       <c r="C584" s="6" t="n"/>
@@ -7243,7 +7243,7 @@
     </row>
     <row r="585" hidden="1" outlineLevel="2">
       <c r="A585" s="4" t="n">
-        <v>144.75</v>
+        <v>145.75</v>
       </c>
       <c r="B585" s="5" t="n"/>
       <c r="C585" s="6" t="n"/>
@@ -7254,7 +7254,7 @@
     </row>
     <row r="586" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A586" s="4" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B586" s="5" t="n"/>
       <c r="C586" s="6" t="n"/>
@@ -7265,7 +7265,7 @@
     </row>
     <row r="587" hidden="1" outlineLevel="2">
       <c r="A587" s="4" t="n">
-        <v>145.25</v>
+        <v>146.25</v>
       </c>
       <c r="B587" s="5" t="n"/>
       <c r="C587" s="6" t="n"/>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="588" hidden="1" outlineLevel="2">
       <c r="A588" s="4" t="n">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="B588" s="5" t="n"/>
       <c r="C588" s="6" t="n"/>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="589" hidden="1" outlineLevel="2">
       <c r="A589" s="4" t="n">
-        <v>145.75</v>
+        <v>146.75</v>
       </c>
       <c r="B589" s="5" t="n"/>
       <c r="C589" s="6" t="n"/>
@@ -7298,7 +7298,7 @@
     </row>
     <row r="590" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A590" s="4" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B590" s="5" t="n"/>
       <c r="C590" s="6" t="n"/>
@@ -7309,7 +7309,7 @@
     </row>
     <row r="591" hidden="1" outlineLevel="2">
       <c r="A591" s="4" t="n">
-        <v>146.25</v>
+        <v>147.25</v>
       </c>
       <c r="B591" s="5" t="n"/>
       <c r="C591" s="6" t="n"/>
@@ -7320,7 +7320,7 @@
     </row>
     <row r="592" hidden="1" outlineLevel="2">
       <c r="A592" s="4" t="n">
-        <v>146.5</v>
+        <v>147.5</v>
       </c>
       <c r="B592" s="5" t="n"/>
       <c r="C592" s="6" t="n"/>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="593" hidden="1" outlineLevel="2">
       <c r="A593" s="4" t="n">
-        <v>146.75</v>
+        <v>147.75</v>
       </c>
       <c r="B593" s="5" t="n"/>
       <c r="C593" s="6" t="n"/>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="594" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A594" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B594" s="5" t="n"/>
       <c r="C594" s="6" t="n"/>
@@ -7353,7 +7353,7 @@
     </row>
     <row r="595" hidden="1" outlineLevel="2">
       <c r="A595" s="4" t="n">
-        <v>147.25</v>
+        <v>148.25</v>
       </c>
       <c r="B595" s="5" t="n"/>
       <c r="C595" s="6" t="n"/>
@@ -7364,7 +7364,7 @@
     </row>
     <row r="596" hidden="1" outlineLevel="2">
       <c r="A596" s="4" t="n">
-        <v>147.5</v>
+        <v>148.5</v>
       </c>
       <c r="B596" s="5" t="n"/>
       <c r="C596" s="6" t="n"/>
@@ -7375,7 +7375,7 @@
     </row>
     <row r="597" hidden="1" outlineLevel="2">
       <c r="A597" s="4" t="n">
-        <v>147.75</v>
+        <v>148.75</v>
       </c>
       <c r="B597" s="5" t="n"/>
       <c r="C597" s="6" t="n"/>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="598" collapsed="1">
       <c r="A598" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B598" s="5" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="599" hidden="1" outlineLevel="2">
       <c r="A599" s="4" t="n">
-        <v>148.25</v>
+        <v>149.25</v>
       </c>
       <c r="B599" s="5" t="n"/>
       <c r="C599" s="6" t="n"/>
@@ -7424,7 +7424,7 @@
     </row>
     <row r="600" hidden="1" outlineLevel="2">
       <c r="A600" s="4" t="n">
-        <v>148.5</v>
+        <v>149.5</v>
       </c>
       <c r="B600" s="5" t="n"/>
       <c r="C600" s="6" t="n"/>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="601" hidden="1" outlineLevel="2">
       <c r="A601" s="4" t="n">
-        <v>148.75</v>
+        <v>149.75</v>
       </c>
       <c r="B601" s="5" t="n"/>
       <c r="C601" s="6" t="n"/>
@@ -7446,7 +7446,7 @@
     </row>
     <row r="602" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A602" s="4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B602" s="5" t="n"/>
       <c r="C602" s="6" t="n"/>
@@ -7457,7 +7457,7 @@
     </row>
     <row r="603" hidden="1" outlineLevel="2">
       <c r="A603" s="4" t="n">
-        <v>149.25</v>
+        <v>150.25</v>
       </c>
       <c r="B603" s="5" t="n"/>
       <c r="C603" s="6" t="n"/>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="604" hidden="1" outlineLevel="2">
       <c r="A604" s="4" t="n">
-        <v>149.5</v>
+        <v>150.5</v>
       </c>
       <c r="B604" s="5" t="n"/>
       <c r="C604" s="6" t="n"/>
@@ -7479,7 +7479,7 @@
     </row>
     <row r="605" hidden="1" outlineLevel="2">
       <c r="A605" s="4" t="n">
-        <v>149.75</v>
+        <v>150.75</v>
       </c>
       <c r="B605" s="5" t="n"/>
       <c r="C605" s="6" t="n"/>
@@ -7490,7 +7490,7 @@
     </row>
     <row r="606" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A606" s="4" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B606" s="5" t="n"/>
       <c r="C606" s="6" t="n"/>
@@ -7501,7 +7501,7 @@
     </row>
     <row r="607" hidden="1" outlineLevel="2">
       <c r="A607" s="4" t="n">
-        <v>150.25</v>
+        <v>151.25</v>
       </c>
       <c r="B607" s="5" t="n"/>
       <c r="C607" s="6" t="n"/>
@@ -7512,7 +7512,7 @@
     </row>
     <row r="608" hidden="1" outlineLevel="2">
       <c r="A608" s="4" t="n">
-        <v>150.5</v>
+        <v>151.5</v>
       </c>
       <c r="B608" s="5" t="n"/>
       <c r="C608" s="6" t="n"/>
@@ -7523,7 +7523,7 @@
     </row>
     <row r="609" hidden="1" outlineLevel="2">
       <c r="A609" s="4" t="n">
-        <v>150.75</v>
+        <v>151.75</v>
       </c>
       <c r="B609" s="5" t="n"/>
       <c r="C609" s="6" t="n"/>
@@ -7534,7 +7534,7 @@
     </row>
     <row r="610" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A610" s="4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B610" s="5" t="n"/>
       <c r="C610" s="6" t="n"/>
@@ -7545,7 +7545,7 @@
     </row>
     <row r="611" hidden="1" outlineLevel="2">
       <c r="A611" s="4" t="n">
-        <v>151.25</v>
+        <v>152.25</v>
       </c>
       <c r="B611" s="5" t="n"/>
       <c r="C611" s="6" t="n"/>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="612" hidden="1" outlineLevel="2">
       <c r="A612" s="4" t="n">
-        <v>151.5</v>
+        <v>152.5</v>
       </c>
       <c r="B612" s="5" t="n"/>
       <c r="C612" s="6" t="n"/>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="613" hidden="1" outlineLevel="2">
       <c r="A613" s="4" t="n">
-        <v>151.75</v>
+        <v>152.75</v>
       </c>
       <c r="B613" s="5" t="n"/>
       <c r="C613" s="6" t="n"/>
@@ -7578,7 +7578,7 @@
     </row>
     <row r="614" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A614" s="4" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B614" s="5" t="n"/>
       <c r="C614" s="6" t="n"/>
@@ -7589,7 +7589,7 @@
     </row>
     <row r="615" hidden="1" outlineLevel="2">
       <c r="A615" s="4" t="n">
-        <v>152.25</v>
+        <v>153.25</v>
       </c>
       <c r="B615" s="5" t="n"/>
       <c r="C615" s="6" t="n"/>
@@ -7600,7 +7600,7 @@
     </row>
     <row r="616" hidden="1" outlineLevel="2">
       <c r="A616" s="4" t="n">
-        <v>152.5</v>
+        <v>153.5</v>
       </c>
       <c r="B616" s="5" t="n"/>
       <c r="C616" s="6" t="n"/>
@@ -7611,7 +7611,7 @@
     </row>
     <row r="617" hidden="1" outlineLevel="2">
       <c r="A617" s="4" t="n">
-        <v>152.75</v>
+        <v>153.75</v>
       </c>
       <c r="B617" s="5" t="n"/>
       <c r="C617" s="6" t="n"/>
@@ -7622,7 +7622,7 @@
     </row>
     <row r="618" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A618" s="4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B618" s="5" t="n"/>
       <c r="C618" s="6" t="n"/>
@@ -7633,7 +7633,7 @@
     </row>
     <row r="619" hidden="1" outlineLevel="2">
       <c r="A619" s="4" t="n">
-        <v>153.25</v>
+        <v>154.25</v>
       </c>
       <c r="B619" s="5" t="n"/>
       <c r="C619" s="6" t="n"/>
@@ -7644,7 +7644,7 @@
     </row>
     <row r="620" hidden="1" outlineLevel="2">
       <c r="A620" s="4" t="n">
-        <v>153.5</v>
+        <v>154.5</v>
       </c>
       <c r="B620" s="5" t="n"/>
       <c r="C620" s="6" t="n"/>
@@ -7655,7 +7655,7 @@
     </row>
     <row r="621" hidden="1" outlineLevel="2">
       <c r="A621" s="4" t="n">
-        <v>153.75</v>
+        <v>154.75</v>
       </c>
       <c r="B621" s="5" t="n"/>
       <c r="C621" s="6" t="n"/>
@@ -7666,7 +7666,7 @@
     </row>
     <row r="622" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A622" s="4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B622" s="5" t="n"/>
       <c r="C622" s="6" t="n"/>
@@ -7677,7 +7677,7 @@
     </row>
     <row r="623" hidden="1" outlineLevel="2">
       <c r="A623" s="4" t="n">
-        <v>154.25</v>
+        <v>155.25</v>
       </c>
       <c r="B623" s="5" t="n"/>
       <c r="C623" s="6" t="n"/>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="624" hidden="1" outlineLevel="2">
       <c r="A624" s="4" t="n">
-        <v>154.5</v>
+        <v>155.5</v>
       </c>
       <c r="B624" s="5" t="n"/>
       <c r="C624" s="6" t="n"/>
@@ -7699,7 +7699,7 @@
     </row>
     <row r="625" hidden="1" outlineLevel="2">
       <c r="A625" s="4" t="n">
-        <v>154.75</v>
+        <v>155.75</v>
       </c>
       <c r="B625" s="5" t="n"/>
       <c r="C625" s="6" t="n"/>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="626" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A626" s="4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B626" s="5" t="n"/>
       <c r="C626" s="6" t="n"/>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="627" hidden="1" outlineLevel="2">
       <c r="A627" s="4" t="n">
-        <v>155.25</v>
+        <v>156.25</v>
       </c>
       <c r="B627" s="5" t="n"/>
       <c r="C627" s="6" t="n"/>
@@ -7732,7 +7732,7 @@
     </row>
     <row r="628" hidden="1" outlineLevel="2">
       <c r="A628" s="4" t="n">
-        <v>155.5</v>
+        <v>156.5</v>
       </c>
       <c r="B628" s="5" t="n"/>
       <c r="C628" s="6" t="n"/>
@@ -7743,7 +7743,7 @@
     </row>
     <row r="629" hidden="1" outlineLevel="2">
       <c r="A629" s="4" t="n">
-        <v>155.75</v>
+        <v>156.75</v>
       </c>
       <c r="B629" s="5" t="n"/>
       <c r="C629" s="6" t="n"/>
@@ -7754,7 +7754,7 @@
     </row>
     <row r="630" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A630" s="4" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B630" s="5" t="n"/>
       <c r="C630" s="6" t="n"/>
@@ -7765,7 +7765,7 @@
     </row>
     <row r="631" hidden="1" outlineLevel="2">
       <c r="A631" s="4" t="n">
-        <v>156.25</v>
+        <v>157.25</v>
       </c>
       <c r="B631" s="5" t="n"/>
       <c r="C631" s="6" t="n"/>
@@ -7776,7 +7776,7 @@
     </row>
     <row r="632" hidden="1" outlineLevel="2">
       <c r="A632" s="4" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="B632" s="5" t="n"/>
       <c r="C632" s="6" t="n"/>
@@ -7787,7 +7787,7 @@
     </row>
     <row r="633" hidden="1" outlineLevel="2">
       <c r="A633" s="4" t="n">
-        <v>156.75</v>
+        <v>157.75</v>
       </c>
       <c r="B633" s="5" t="n"/>
       <c r="C633" s="6" t="n"/>
@@ -7798,7 +7798,7 @@
     </row>
     <row r="634" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A634" s="4" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B634" s="5" t="n"/>
       <c r="C634" s="6" t="n"/>
@@ -7809,7 +7809,7 @@
     </row>
     <row r="635" hidden="1" outlineLevel="2">
       <c r="A635" s="4" t="n">
-        <v>157.25</v>
+        <v>158.25</v>
       </c>
       <c r="B635" s="5" t="n"/>
       <c r="C635" s="6" t="n"/>
@@ -7820,7 +7820,7 @@
     </row>
     <row r="636" hidden="1" outlineLevel="2">
       <c r="A636" s="4" t="n">
-        <v>157.5</v>
+        <v>158.5</v>
       </c>
       <c r="B636" s="5" t="n"/>
       <c r="C636" s="6" t="n"/>
@@ -7831,7 +7831,7 @@
     </row>
     <row r="637" hidden="1" outlineLevel="2">
       <c r="A637" s="4" t="n">
-        <v>157.75</v>
+        <v>158.75</v>
       </c>
       <c r="B637" s="5" t="n"/>
       <c r="C637" s="6" t="n"/>
@@ -7842,7 +7842,7 @@
     </row>
     <row r="638" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A638" s="4" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B638" s="5" t="n"/>
       <c r="C638" s="6" t="n"/>
@@ -7853,7 +7853,7 @@
     </row>
     <row r="639" hidden="1" outlineLevel="2">
       <c r="A639" s="4" t="n">
-        <v>158.25</v>
+        <v>159.25</v>
       </c>
       <c r="B639" s="5" t="n"/>
       <c r="C639" s="6" t="n"/>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="640" hidden="1" outlineLevel="2">
       <c r="A640" s="4" t="n">
-        <v>158.5</v>
+        <v>159.5</v>
       </c>
       <c r="B640" s="5" t="n"/>
       <c r="C640" s="6" t="n"/>
@@ -7875,7 +7875,7 @@
     </row>
     <row r="641" hidden="1" outlineLevel="2">
       <c r="A641" s="4" t="n">
-        <v>158.75</v>
+        <v>159.75</v>
       </c>
       <c r="B641" s="5" t="n"/>
       <c r="C641" s="6" t="n"/>
@@ -7886,7 +7886,7 @@
     </row>
     <row r="642" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A642" s="4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B642" s="5" t="n"/>
       <c r="C642" s="6" t="n"/>
@@ -7897,7 +7897,7 @@
     </row>
     <row r="643" hidden="1" outlineLevel="2">
       <c r="A643" s="4" t="n">
-        <v>159.25</v>
+        <v>160.25</v>
       </c>
       <c r="B643" s="5" t="n"/>
       <c r="C643" s="6" t="n"/>
@@ -7908,7 +7908,7 @@
     </row>
     <row r="644" hidden="1" outlineLevel="2">
       <c r="A644" s="4" t="n">
-        <v>159.5</v>
+        <v>160.5</v>
       </c>
       <c r="B644" s="5" t="n"/>
       <c r="C644" s="6" t="n"/>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="645" hidden="1" outlineLevel="2">
       <c r="A645" s="4" t="n">
-        <v>159.75</v>
+        <v>160.75</v>
       </c>
       <c r="B645" s="5" t="n"/>
       <c r="C645" s="6" t="n"/>
@@ -7930,7 +7930,7 @@
     </row>
     <row r="646">
       <c r="A646" s="7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
